--- a/input_processing/clean_excel_files_PL/reg_home_ownership.xlsx
+++ b/input_processing/clean_excel_files_PL/reg_home_ownership.xlsx
@@ -412,7 +412,7 @@
         <v>17</v>
       </c>
       <c r="B5" s="1">
-        <v>0.89489578556752658</v>
+        <v>0.89489622130564206</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -420,7 +420,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="1">
-        <v>23243.354381519712</v>
+        <v>23242.242354515576</v>
       </c>
     </row>
     <row r="6">
@@ -436,7 +436,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="1">
-        <v>-7873379.9400775526</v>
+        <v>-7873347.2988389907</v>
       </c>
     </row>
   </sheetData>
@@ -560,106 +560,106 @@
         <v>27</v>
       </c>
       <c r="B2" s="1">
-        <v>0.0055217826555176248</v>
+        <v>0.0055157342282533576</v>
       </c>
       <c r="C2" s="1">
-        <v>0.0010253012026944814</v>
+        <v>0.0010252594138144085</v>
       </c>
       <c r="D2" s="1">
-        <v>1.0187625757063546e-05</v>
+        <v>1.0191454040448906e-05</v>
       </c>
       <c r="E2" s="1">
-        <v>-5.1819841306968236e-08</v>
+        <v>-5.1870380050491372e-08</v>
       </c>
       <c r="F2" s="1">
-        <v>-0.00043608654354639423</v>
+        <v>-0.00043600218785022334</v>
       </c>
       <c r="G2" s="1">
-        <v>-0.00024950237754996202</v>
+        <v>-0.00024942001618827027</v>
       </c>
       <c r="H2" s="1">
-        <v>5.6852602415642303e-05</v>
+        <v>5.6838252213923493e-05</v>
       </c>
       <c r="I2" s="1">
-        <v>-0.0002066375253355959</v>
+        <v>-0.00020658690294756527</v>
       </c>
       <c r="J2" s="1">
-        <v>-0.00026005812105714811</v>
+        <v>-0.00026006802014255496</v>
       </c>
       <c r="K2" s="1">
-        <v>0.00011517777087979501</v>
+        <v>0.00011519149819323912</v>
       </c>
       <c r="L2" s="1">
-        <v>0.00052108024386409162</v>
+        <v>0.00052103688379686881</v>
       </c>
       <c r="M2" s="1">
-        <v>0.00026211477751951511</v>
+        <v>0.00026209919399141545</v>
       </c>
       <c r="N2" s="1">
-        <v>7.5024814481137894e-05</v>
+        <v>7.5076537876437547e-05</v>
       </c>
       <c r="O2" s="1">
-        <v>-0.00014631348433018985</v>
+        <v>-0.00014628448021894189</v>
       </c>
       <c r="P2" s="1">
-        <v>-0.0001504226716678639</v>
+        <v>-0.00015036823599548759</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7240655321596647e-05</v>
+        <v>1.7348881433997768e-05</v>
       </c>
       <c r="R2" s="1">
-        <v>-0.00011910932376519269</v>
+        <v>-0.00011910365070319105</v>
       </c>
       <c r="S2" s="1">
-        <v>-0.00011571601765513991</v>
+        <v>-0.00011556486340071542</v>
       </c>
       <c r="T2" s="1">
-        <v>-4.4243441594144758e-05</v>
+        <v>-4.4150971816155586e-05</v>
       </c>
       <c r="U2" s="1">
-        <v>-0.00013956468224718914</v>
+        <v>-0.00013951098953446324</v>
       </c>
       <c r="V2" s="1">
-        <v>1.9425490343522579e-05</v>
+        <v>2.0266321623504547e-05</v>
       </c>
       <c r="W2" s="1">
-        <v>8.5813084666958733e-05</v>
+        <v>8.6222217475913961e-05</v>
       </c>
       <c r="X2" s="1">
-        <v>-9.5717077923459059e-06</v>
+        <v>-9.1485995945669437e-06</v>
       </c>
       <c r="Y2" s="1">
-        <v>-5.1490530926505081e-05</v>
+        <v>-5.1061133848233744e-05</v>
       </c>
       <c r="Z2" s="1">
-        <v>1.7043880377796739e-05</v>
+        <v>1.703249624486109e-05</v>
       </c>
       <c r="AA2" s="1">
-        <v>1.2655537415415209e-06</v>
+        <v>1.2971106044525288e-06</v>
       </c>
       <c r="AB2" s="1">
-        <v>0.00013356223390172865</v>
+        <v>0.00013348757485753875</v>
       </c>
       <c r="AC2" s="1">
-        <v>3.6018549702649739e-05</v>
+        <v>3.5906606022980759e-05</v>
       </c>
       <c r="AD2" s="1">
-        <v>8.4478008515147991e-05</v>
+        <v>8.4432833747047036e-05</v>
       </c>
       <c r="AE2" s="1">
-        <v>7.6695965527998262e-05</v>
+        <v>7.6617553245312344e-05</v>
       </c>
       <c r="AF2" s="1">
-        <v>4.1541907824473162e-06</v>
+        <v>4.1526504448567318e-06</v>
       </c>
       <c r="AG2" s="1">
-        <v>0.00020710799942020956</v>
+        <v>0.00020691904777094027</v>
       </c>
       <c r="AH2" s="1">
-        <v>-8.3857411505204268e-06</v>
+        <v>-8.3485432470863487e-06</v>
       </c>
       <c r="AI2" s="1">
-        <v>-0.0010097613556004923</v>
+        <v>-0.0010102824590421881</v>
       </c>
     </row>
     <row r="3">
@@ -667,106 +667,106 @@
         <v>28</v>
       </c>
       <c r="B3" s="1">
-        <v>-0.001333356576814426</v>
+        <v>-0.0013327988363437714</v>
       </c>
       <c r="C3" s="1">
-        <v>1.0187625757063546e-05</v>
+        <v>1.0191454040448906e-05</v>
       </c>
       <c r="D3" s="1">
-        <v>2.8024261893260016e-05</v>
+        <v>2.8023250855985038e-05</v>
       </c>
       <c r="E3" s="1">
-        <v>-2.557974826879667e-07</v>
+        <v>-2.5578316094875012e-07</v>
       </c>
       <c r="F3" s="1">
-        <v>7.1181163033788206e-05</v>
+        <v>7.1163406494817905e-05</v>
       </c>
       <c r="G3" s="1">
-        <v>1.3308979753285814e-05</v>
+        <v>1.3288268750287241e-05</v>
       </c>
       <c r="H3" s="1">
-        <v>3.6199300382121734e-05</v>
+        <v>3.6193057995715608e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>0.00010938316690686529</v>
+        <v>0.00010936905913157735</v>
       </c>
       <c r="J3" s="1">
-        <v>1.4520820285246158e-05</v>
+        <v>1.45177269526193e-05</v>
       </c>
       <c r="K3" s="1">
-        <v>3.15622655372736e-05</v>
+        <v>3.1558733915692283e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>2.1123565515370109e-05</v>
+        <v>2.1125033725385886e-05</v>
       </c>
       <c r="M3" s="1">
-        <v>0.00015347794856690878</v>
+        <v>0.00015348692503866002</v>
       </c>
       <c r="N3" s="1">
-        <v>1.7997351592592372e-05</v>
+        <v>1.7989508519135919e-05</v>
       </c>
       <c r="O3" s="1">
-        <v>-2.4300747964118004e-05</v>
+        <v>-2.4334805518614811e-05</v>
       </c>
       <c r="P3" s="1">
-        <v>-3.2200531772687486e-05</v>
+        <v>-3.2218804070045771e-05</v>
       </c>
       <c r="Q3" s="1">
-        <v>-1.2529695370788675e-05</v>
+        <v>-1.2558686222294182e-05</v>
       </c>
       <c r="R3" s="1">
-        <v>-3.7453550226100178e-05</v>
+        <v>-3.7458337694319942e-05</v>
       </c>
       <c r="S3" s="1">
-        <v>-6.4163424380623933e-05</v>
+        <v>-6.4187775410812898e-05</v>
       </c>
       <c r="T3" s="1">
-        <v>-3.6155691423951475e-05</v>
+        <v>-3.6167407837847635e-05</v>
       </c>
       <c r="U3" s="1">
-        <v>4.6209794408663706e-05</v>
+        <v>4.6199514972125296e-05</v>
       </c>
       <c r="V3" s="1">
-        <v>1.9751837622613978e-05</v>
+        <v>1.9601045053726636e-05</v>
       </c>
       <c r="W3" s="1">
-        <v>-2.8904253519728627e-05</v>
+        <v>-2.8975039892373462e-05</v>
       </c>
       <c r="X3" s="1">
-        <v>-1.4746219871119735e-05</v>
+        <v>-1.4819559859276277e-05</v>
       </c>
       <c r="Y3" s="1">
-        <v>-3.334311200503667e-05</v>
+        <v>-3.341954907391993e-05</v>
       </c>
       <c r="Z3" s="1">
-        <v>2.4380910270669666e-06</v>
+        <v>2.440504676227692e-06</v>
       </c>
       <c r="AA3" s="1">
-        <v>-2.3135685107409824e-06</v>
+        <v>-2.318174994157254e-06</v>
       </c>
       <c r="AB3" s="1">
-        <v>-1.624120138801413e-05</v>
+        <v>-1.6219783736747039e-05</v>
       </c>
       <c r="AC3" s="1">
-        <v>9.9722643640448886e-07</v>
+        <v>1.0020687029202533e-06</v>
       </c>
       <c r="AD3" s="1">
-        <v>1.7766853539537218e-06</v>
+        <v>1.7928452363512139e-06</v>
       </c>
       <c r="AE3" s="1">
-        <v>8.487245207729015e-07</v>
+        <v>8.6128256701267975e-07</v>
       </c>
       <c r="AF3" s="1">
-        <v>8.9705994768908749e-07</v>
+        <v>8.9566468710405384e-07</v>
       </c>
       <c r="AG3" s="1">
-        <v>-3.9228291597210663e-05</v>
+        <v>-3.9222352389803533e-05</v>
       </c>
       <c r="AH3" s="1">
-        <v>-5.3401001829849002e-06</v>
+        <v>-5.3287448089275056e-06</v>
       </c>
       <c r="AI3" s="1">
-        <v>-0.00066625676152621736</v>
+        <v>-0.0006661271581462761</v>
       </c>
     </row>
     <row r="4">
@@ -774,106 +774,106 @@
         <v>29</v>
       </c>
       <c r="B4" s="1">
-        <v>-8.7873529780962816e-06</v>
+        <v>-8.7829294148481599e-06</v>
       </c>
       <c r="C4" s="1">
-        <v>-5.1819841306968236e-08</v>
+        <v>-5.1870380050491372e-08</v>
       </c>
       <c r="D4" s="1">
-        <v>-2.557974826879667e-07</v>
+        <v>-2.5578316094875012e-07</v>
       </c>
       <c r="E4" s="1">
-        <v>2.4437638512658298e-09</v>
+        <v>2.4435762818119593e-09</v>
       </c>
       <c r="F4" s="1">
-        <v>-5.3958153257519997e-07</v>
+        <v>-5.3939900960649463e-07</v>
       </c>
       <c r="G4" s="1">
-        <v>-2.1003806880845878e-07</v>
+        <v>-2.0980653889843693e-07</v>
       </c>
       <c r="H4" s="1">
-        <v>-2.2190619506743957e-07</v>
+        <v>-2.2183591604126616e-07</v>
       </c>
       <c r="I4" s="1">
-        <v>-8.773062271772375e-07</v>
+        <v>-8.7714991014095637e-07</v>
       </c>
       <c r="J4" s="1">
-        <v>-4.5019195706814538e-08</v>
+        <v>-4.4967711604994202e-08</v>
       </c>
       <c r="K4" s="1">
-        <v>-2.3780927825340882e-07</v>
+        <v>-2.3777300363348163e-07</v>
       </c>
       <c r="L4" s="1">
-        <v>-1.1604788968772363e-08</v>
+        <v>-1.1614914391957423e-08</v>
       </c>
       <c r="M4" s="1">
-        <v>-1.2296513467831838e-06</v>
+        <v>-1.2296955408606344e-06</v>
       </c>
       <c r="N4" s="1">
-        <v>-2.4044850694781615e-07</v>
+        <v>-2.4035720670042705e-07</v>
       </c>
       <c r="O4" s="1">
-        <v>2.5102399187074278e-07</v>
+        <v>2.5134188905756324e-07</v>
       </c>
       <c r="P4" s="1">
-        <v>3.0893369107711901e-07</v>
+        <v>3.0910166094041475e-07</v>
       </c>
       <c r="Q4" s="1">
-        <v>3.4984838443742284e-08</v>
+        <v>3.533200603852238e-08</v>
       </c>
       <c r="R4" s="1">
-        <v>3.6595427758275255e-07</v>
+        <v>3.6597968877485047e-07</v>
       </c>
       <c r="S4" s="1">
-        <v>6.743524837525216e-07</v>
+        <v>6.7452758240166234e-07</v>
       </c>
       <c r="T4" s="1">
-        <v>4.6072195654517022e-07</v>
+        <v>4.608174562541542e-07</v>
       </c>
       <c r="U4" s="1">
-        <v>-1.9020991839300092e-07</v>
+        <v>-1.9013421465907751e-07</v>
       </c>
       <c r="V4" s="1">
-        <v>-1.761401030226397e-07</v>
+        <v>-1.7467584370420078e-07</v>
       </c>
       <c r="W4" s="1">
-        <v>2.9374673972222272e-07</v>
+        <v>2.9444189595068111e-07</v>
       </c>
       <c r="X4" s="1">
-        <v>1.9038412980075187e-07</v>
+        <v>1.9111069301303631e-07</v>
       </c>
       <c r="Y4" s="1">
-        <v>3.3691857230022928e-07</v>
+        <v>3.3768330183125659e-07</v>
       </c>
       <c r="Z4" s="1">
-        <v>-1.8855388583301745e-08</v>
+        <v>-1.8880896116437346e-08</v>
       </c>
       <c r="AA4" s="1">
-        <v>-1.577508248251216e-08</v>
+        <v>-1.5730525886711247e-08</v>
       </c>
       <c r="AB4" s="1">
-        <v>2.1722774254655125e-07</v>
+        <v>2.1697693665274262e-07</v>
       </c>
       <c r="AC4" s="1">
-        <v>-5.2305234655144031e-08</v>
+        <v>-5.233432742782789e-08</v>
       </c>
       <c r="AD4" s="1">
-        <v>-1.7726683394529271e-08</v>
+        <v>-1.7861251314963683e-08</v>
       </c>
       <c r="AE4" s="1">
-        <v>-3.3882558595311323e-08</v>
+        <v>-3.3990372793663547e-08</v>
       </c>
       <c r="AF4" s="1">
-        <v>-8.7979821706091228e-09</v>
+        <v>-8.7858198841563254e-09</v>
       </c>
       <c r="AG4" s="1">
-        <v>4.8566585989150069e-07</v>
+        <v>4.8555487422392973e-07</v>
       </c>
       <c r="AH4" s="1">
-        <v>3.5739417960129928e-08</v>
+        <v>3.5637235456300244e-08</v>
       </c>
       <c r="AI4" s="1">
-        <v>5.6242570610441148e-06</v>
+        <v>5.6229433024775484e-06</v>
       </c>
     </row>
     <row r="5">
@@ -881,106 +881,106 @@
         <v>30</v>
       </c>
       <c r="B5" s="1">
-        <v>-0.97224848228394711</v>
+        <v>-0.97225882683510245</v>
       </c>
       <c r="C5" s="1">
-        <v>-0.00043608654354639423</v>
+        <v>-0.00043600218785022334</v>
       </c>
       <c r="D5" s="1">
-        <v>7.1181163033788206e-05</v>
+        <v>7.1163406494817905e-05</v>
       </c>
       <c r="E5" s="1">
-        <v>-5.3958153257519997e-07</v>
+        <v>-5.3939900960649463e-07</v>
       </c>
       <c r="F5" s="1">
-        <v>0.1097933546569074</v>
+        <v>0.10979160583869779</v>
       </c>
       <c r="G5" s="1">
-        <v>0.0044397473498215892</v>
+        <v>0.0044399184923545748</v>
       </c>
       <c r="H5" s="1">
-        <v>0.0048664171591475177</v>
+        <v>0.0048666629577598132</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0049051709764105309</v>
+        <v>0.0049053100475428399</v>
       </c>
       <c r="J5" s="1">
-        <v>0.0048253727071790259</v>
+        <v>0.0048256123750957374</v>
       </c>
       <c r="K5" s="1">
-        <v>0.0046703214728683693</v>
+        <v>0.0046705838121677955</v>
       </c>
       <c r="L5" s="1">
-        <v>0.0048721464073992454</v>
+        <v>0.0048725567351219357</v>
       </c>
       <c r="M5" s="1">
-        <v>0.00032968851069084651</v>
+        <v>0.00032965518784308287</v>
       </c>
       <c r="N5" s="1">
-        <v>-0.00020113653727649432</v>
+        <v>-0.00020111028281137242</v>
       </c>
       <c r="O5" s="1">
-        <v>0.0009304033297670869</v>
+        <v>0.00093052771640258298</v>
       </c>
       <c r="P5" s="1">
-        <v>0.00063368203544821164</v>
+        <v>0.00063374456441793719</v>
       </c>
       <c r="Q5" s="1">
-        <v>0.00037745976610460046</v>
+        <v>0.00037753649611796695</v>
       </c>
       <c r="R5" s="1">
-        <v>1.6870920753296733e-05</v>
+        <v>1.6826716591518062e-05</v>
       </c>
       <c r="S5" s="1">
-        <v>-6.6851619706022217e-06</v>
+        <v>-6.9205031003239281e-06</v>
       </c>
       <c r="T5" s="1">
-        <v>-1.7928582155086678e-06</v>
+        <v>-1.9980754949638132e-06</v>
       </c>
       <c r="U5" s="1">
-        <v>-0.00048788255669139115</v>
+        <v>-0.00048802717102153659</v>
       </c>
       <c r="V5" s="1">
-        <v>6.9706558135713536e-05</v>
+        <v>6.9283174307708086e-05</v>
       </c>
       <c r="W5" s="1">
-        <v>9.0411189599724903e-05</v>
+        <v>9.0355876388349774e-05</v>
       </c>
       <c r="X5" s="1">
-        <v>0.00014358080305102033</v>
+        <v>0.00014352091070718423</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.00069832211350723261</v>
+        <v>0.00069835057831639773</v>
       </c>
       <c r="Z5" s="1">
-        <v>-0.00011809867867808874</v>
+        <v>-0.00011812177465150039</v>
       </c>
       <c r="AA5" s="1">
-        <v>-0.00032910284523235661</v>
+        <v>-0.00032914750589769473</v>
       </c>
       <c r="AB5" s="1">
-        <v>0.0001324009512291913</v>
+        <v>0.00013258464283199146</v>
       </c>
       <c r="AC5" s="1">
-        <v>-0.00013050618218950379</v>
+        <v>-0.00013031174901085435</v>
       </c>
       <c r="AD5" s="1">
-        <v>-0.00020840439676645238</v>
+        <v>-0.00020830371312508393</v>
       </c>
       <c r="AE5" s="1">
-        <v>-0.00030774076146367893</v>
+        <v>-0.00030765779270407038</v>
       </c>
       <c r="AF5" s="1">
-        <v>-6.5319551372293406e-06</v>
+        <v>-6.5349142992832988e-06</v>
       </c>
       <c r="AG5" s="1">
-        <v>-0.0003190860430732842</v>
+        <v>-0.00031898105588199291</v>
       </c>
       <c r="AH5" s="1">
-        <v>0.00039326736813395636</v>
+        <v>0.00039329865480916722</v>
       </c>
       <c r="AI5" s="1">
-        <v>-0.0063816626722095846</v>
+        <v>-0.006381416873424613</v>
       </c>
     </row>
     <row r="6">
@@ -988,106 +988,106 @@
         <v>31</v>
       </c>
       <c r="B6" s="1">
-        <v>-0.13768588883008309</v>
+        <v>-0.13770430943472822</v>
       </c>
       <c r="C6" s="1">
-        <v>-0.00024950237754996202</v>
+        <v>-0.00024942001618827027</v>
       </c>
       <c r="D6" s="1">
-        <v>1.3308979753285814e-05</v>
+        <v>1.3288268750287241e-05</v>
       </c>
       <c r="E6" s="1">
-        <v>-2.1003806880845878e-07</v>
+        <v>-2.0980653889843693e-07</v>
       </c>
       <c r="F6" s="1">
-        <v>0.0044397473498215892</v>
+        <v>0.0044399184923545748</v>
       </c>
       <c r="G6" s="1">
-        <v>0.0057431141419073354</v>
+        <v>0.0057433127985736399</v>
       </c>
       <c r="H6" s="1">
-        <v>0.0044913325770045975</v>
+        <v>0.0044915430423580847</v>
       </c>
       <c r="I6" s="1">
-        <v>0.0042043872491003909</v>
+        <v>0.0042045762970391301</v>
       </c>
       <c r="J6" s="1">
-        <v>0.0046284327506195414</v>
+        <v>0.0046286761123206111</v>
       </c>
       <c r="K6" s="1">
-        <v>0.0047571737385850767</v>
+        <v>0.0047574262000728848</v>
       </c>
       <c r="L6" s="1">
-        <v>0.0045825897308364779</v>
+        <v>0.0045829281155009187</v>
       </c>
       <c r="M6" s="1">
-        <v>8.9906585172103132e-05</v>
+        <v>8.9897160670459844e-05</v>
       </c>
       <c r="N6" s="1">
-        <v>-1.8724369603991854e-05</v>
+        <v>-1.8639634497153584e-05</v>
       </c>
       <c r="O6" s="1">
-        <v>8.4920763309930555e-05</v>
+        <v>8.4867856535652435e-05</v>
       </c>
       <c r="P6" s="1">
-        <v>8.7234997166764795e-05</v>
+        <v>8.7168953832682857e-05</v>
       </c>
       <c r="Q6" s="1">
-        <v>0.00023429618317245371</v>
+        <v>0.00023407842635696121</v>
       </c>
       <c r="R6" s="1">
-        <v>0.00019790487078574759</v>
+        <v>0.00019817852710917784</v>
       </c>
       <c r="S6" s="1">
-        <v>9.0251582091518636e-05</v>
+        <v>9.0550624057554987e-05</v>
       </c>
       <c r="T6" s="1">
-        <v>0.00010935153787801469</v>
+        <v>0.00010963545907553195</v>
       </c>
       <c r="U6" s="1">
-        <v>-1.9141193785483183e-05</v>
+        <v>-1.8883731247236295e-05</v>
       </c>
       <c r="V6" s="1">
-        <v>2.1074563161249562e-05</v>
+        <v>2.2699021009721571e-05</v>
       </c>
       <c r="W6" s="1">
-        <v>0.00024558685069701956</v>
+        <v>0.00024646928154228095</v>
       </c>
       <c r="X6" s="1">
-        <v>0.0005836356999005674</v>
+        <v>0.00058453139797889073</v>
       </c>
       <c r="Y6" s="1">
-        <v>0.0014808570481202338</v>
+        <v>0.0014818280495099978</v>
       </c>
       <c r="Z6" s="1">
-        <v>-5.3621536081370708e-05</v>
+        <v>-5.3661474261808658e-05</v>
       </c>
       <c r="AA6" s="1">
-        <v>-0.00014017992309831357</v>
+        <v>-0.00014013264826896079</v>
       </c>
       <c r="AB6" s="1">
-        <v>3.8504958845782906e-05</v>
+        <v>3.8600171725805413e-05</v>
       </c>
       <c r="AC6" s="1">
-        <v>0.00019367917905725143</v>
+        <v>0.00019358904626544686</v>
       </c>
       <c r="AD6" s="1">
-        <v>-5.157229170116767e-06</v>
+        <v>-4.8643516756680105e-06</v>
       </c>
       <c r="AE6" s="1">
-        <v>-3.1585154077989289e-05</v>
+        <v>-3.1518877984254437e-05</v>
       </c>
       <c r="AF6" s="1">
-        <v>-3.1270047416422043e-06</v>
+        <v>-3.1219584513314026e-06</v>
       </c>
       <c r="AG6" s="1">
-        <v>-9.9578717831078772e-05</v>
+        <v>-9.9466753123144021e-05</v>
       </c>
       <c r="AH6" s="1">
-        <v>0.0002514476091574786</v>
+        <v>0.000251343665151181</v>
       </c>
       <c r="AI6" s="1">
-        <v>-0.0049778879366692112</v>
+        <v>-0.0049790548579980113</v>
       </c>
     </row>
     <row r="7">
@@ -1095,106 +1095,106 @@
         <v>32</v>
       </c>
       <c r="B7" s="1">
-        <v>-0.17334083318999111</v>
+        <v>-0.17335328619202539</v>
       </c>
       <c r="C7" s="1">
-        <v>5.6852602415642303e-05</v>
+        <v>5.6838252213923493e-05</v>
       </c>
       <c r="D7" s="1">
-        <v>3.6199300382121734e-05</v>
+        <v>3.6193057995715608e-05</v>
       </c>
       <c r="E7" s="1">
-        <v>-2.2190619506743957e-07</v>
+        <v>-2.2183591604126616e-07</v>
       </c>
       <c r="F7" s="1">
-        <v>0.0048664171591475177</v>
+        <v>0.0048666629577598132</v>
       </c>
       <c r="G7" s="1">
-        <v>0.0044913325770045975</v>
+        <v>0.0044915430423580847</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0084814982892697441</v>
+        <v>0.0084818941078090501</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0047485985545689139</v>
+        <v>0.0047488382056203472</v>
       </c>
       <c r="J7" s="1">
-        <v>0.0048928664358673761</v>
+        <v>0.0048931055679471668</v>
       </c>
       <c r="K7" s="1">
-        <v>0.0046295153842094323</v>
+        <v>0.004629777184357955</v>
       </c>
       <c r="L7" s="1">
-        <v>0.0050716875864671631</v>
+        <v>0.0050719893959313422</v>
       </c>
       <c r="M7" s="1">
-        <v>0.00073491890253591773</v>
+        <v>0.00073492372372894717</v>
       </c>
       <c r="N7" s="1">
-        <v>0.00014224469237861096</v>
+        <v>0.00014228108393574091</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.00022841115384627392</v>
+        <v>-0.00022839924974783201</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.0001746491289784549</v>
+        <v>-0.00017463863299571267</v>
       </c>
       <c r="Q7" s="1">
-        <v>-0.00019666709986702348</v>
+        <v>-0.00019673234002288357</v>
       </c>
       <c r="R7" s="1">
-        <v>7.9129888550110274e-05</v>
+        <v>7.8888135405267125e-05</v>
       </c>
       <c r="S7" s="1">
-        <v>4.7007695912139227e-05</v>
+        <v>4.6738658598921302e-05</v>
       </c>
       <c r="T7" s="1">
-        <v>-9.9721893548893015e-05</v>
+        <v>-9.9915069139753826e-05</v>
       </c>
       <c r="U7" s="1">
-        <v>0.00052111786338064235</v>
+        <v>0.00052088613542927188</v>
       </c>
       <c r="V7" s="1">
-        <v>6.3704198917015928e-05</v>
+        <v>6.4363720871313441e-05</v>
       </c>
       <c r="W7" s="1">
-        <v>6.7547684784843246e-05</v>
+        <v>6.7937465402927361e-05</v>
       </c>
       <c r="X7" s="1">
-        <v>8.0538657238699574e-05</v>
+        <v>8.0889674896212867e-05</v>
       </c>
       <c r="Y7" s="1">
-        <v>0.0012406439888905277</v>
+        <v>0.0012411451432060745</v>
       </c>
       <c r="Z7" s="1">
-        <v>-7.6257997809397375e-05</v>
+        <v>-7.6287437757082831e-05</v>
       </c>
       <c r="AA7" s="1">
-        <v>5.4140611069456422e-05</v>
+        <v>5.4185832681908177e-05</v>
       </c>
       <c r="AB7" s="1">
-        <v>0.0008313003445649704</v>
+        <v>0.00083129357871324604</v>
       </c>
       <c r="AC7" s="1">
-        <v>0.00012474809821146592</v>
+        <v>0.00012496038602730769</v>
       </c>
       <c r="AD7" s="1">
-        <v>7.8688988978744021e-05</v>
+        <v>7.8889996787906999e-05</v>
       </c>
       <c r="AE7" s="1">
-        <v>-0.00029993085834891637</v>
+        <v>-0.00029987477499125682</v>
       </c>
       <c r="AF7" s="1">
-        <v>-1.4384790905600252e-05</v>
+        <v>-1.4403622927687722e-05</v>
       </c>
       <c r="AG7" s="1">
-        <v>0.0015306419737571133</v>
+        <v>0.0015307312507497018</v>
       </c>
       <c r="AH7" s="1">
-        <v>0.00039073934265809783</v>
+        <v>0.00039085327887158417</v>
       </c>
       <c r="AI7" s="1">
-        <v>-0.0060068388825839109</v>
+        <v>-0.0060069151409389548</v>
       </c>
     </row>
     <row r="8">
@@ -1202,106 +1202,106 @@
         <v>33</v>
       </c>
       <c r="B8" s="1">
-        <v>1.0523131710439801</v>
+        <v>1.0522781841947104</v>
       </c>
       <c r="C8" s="1">
-        <v>-0.0002066375253355959</v>
+        <v>-0.00020658690294756527</v>
       </c>
       <c r="D8" s="1">
-        <v>0.00010938316690686529</v>
+        <v>0.00010936905913157735</v>
       </c>
       <c r="E8" s="1">
-        <v>-8.773062271772375e-07</v>
+        <v>-8.7714991014095637e-07</v>
       </c>
       <c r="F8" s="1">
-        <v>0.0049051709764105309</v>
+        <v>0.0049053100475428399</v>
       </c>
       <c r="G8" s="1">
-        <v>0.0042043872491003909</v>
+        <v>0.0042045762970391301</v>
       </c>
       <c r="H8" s="1">
-        <v>0.0047485985545689139</v>
+        <v>0.0047488382056203472</v>
       </c>
       <c r="I8" s="1">
-        <v>0.28026405638596946</v>
+        <v>0.28025707937620936</v>
       </c>
       <c r="J8" s="1">
-        <v>0.0046780752021496315</v>
+        <v>0.0046782410828247059</v>
       </c>
       <c r="K8" s="1">
-        <v>0.0043838530048954652</v>
+        <v>0.0043840760017050708</v>
       </c>
       <c r="L8" s="1">
-        <v>0.0048788550422076823</v>
+        <v>0.0048791707170408281</v>
       </c>
       <c r="M8" s="1">
-        <v>0.0014106376538499483</v>
+        <v>0.0014105312585434987</v>
       </c>
       <c r="N8" s="1">
-        <v>0.00010525573173797995</v>
+        <v>0.00010529295631741056</v>
       </c>
       <c r="O8" s="1">
-        <v>-0.0001760664255580866</v>
+        <v>-0.00017598884206392865</v>
       </c>
       <c r="P8" s="1">
-        <v>-0.00029686071200720702</v>
+        <v>-0.00029689086097268872</v>
       </c>
       <c r="Q8" s="1">
-        <v>-0.00024166527585912619</v>
+        <v>-0.00024166471060033893</v>
       </c>
       <c r="R8" s="1">
-        <v>2.1342656319985054e-05</v>
+        <v>2.1079921182893657e-05</v>
       </c>
       <c r="S8" s="1">
-        <v>8.6067423509884119e-05</v>
+        <v>8.5677321705828629e-05</v>
       </c>
       <c r="T8" s="1">
-        <v>7.1910875513445821e-05</v>
+        <v>7.1637821218662563e-05</v>
       </c>
       <c r="U8" s="1">
-        <v>0.00022486736374569905</v>
+        <v>0.00022466256521953831</v>
       </c>
       <c r="V8" s="1">
-        <v>0.0001614831541827316</v>
+        <v>0.00016186809643131499</v>
       </c>
       <c r="W8" s="1">
-        <v>5.1026576590597773e-05</v>
+        <v>5.1314993713701389e-05</v>
       </c>
       <c r="X8" s="1">
-        <v>0.00057013382160985091</v>
+        <v>0.00057038861723722847</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.0012816677600039558</v>
+        <v>0.0012820537542992116</v>
       </c>
       <c r="Z8" s="1">
-        <v>-0.00018331739696391623</v>
+        <v>-0.00018333719713183163</v>
       </c>
       <c r="AA8" s="1">
-        <v>0.00029842096755970313</v>
+        <v>0.00029842893781968118</v>
       </c>
       <c r="AB8" s="1">
-        <v>0.0008007981067031573</v>
+        <v>0.00080104943008802148</v>
       </c>
       <c r="AC8" s="1">
-        <v>3.8953113062006797e-05</v>
+        <v>3.9326919599426673e-05</v>
       </c>
       <c r="AD8" s="1">
-        <v>-5.3559941448758598e-05</v>
+        <v>-5.3285898904157776e-05</v>
       </c>
       <c r="AE8" s="1">
-        <v>-0.00013394412750209568</v>
+        <v>-0.00013376227481682636</v>
       </c>
       <c r="AF8" s="1">
-        <v>4.1096559598746316e-05</v>
+        <v>4.1076569387497571e-05</v>
       </c>
       <c r="AG8" s="1">
-        <v>-0.00017382711948333088</v>
+        <v>-0.00017362786738672059</v>
       </c>
       <c r="AH8" s="1">
-        <v>-8.6370272870860999e-05</v>
+        <v>-8.6228794914914968e-05</v>
       </c>
       <c r="AI8" s="1">
-        <v>-0.0083276544871487054</v>
+        <v>-0.008327474924793939</v>
       </c>
     </row>
     <row r="9">
@@ -1309,106 +1309,106 @@
         <v>34</v>
       </c>
       <c r="B9" s="1">
-        <v>-0.22351645500713901</v>
+        <v>-0.22354682195278996</v>
       </c>
       <c r="C9" s="1">
-        <v>-0.00026005812105714811</v>
+        <v>-0.00026006802014255496</v>
       </c>
       <c r="D9" s="1">
-        <v>1.4520820285246158e-05</v>
+        <v>1.45177269526193e-05</v>
       </c>
       <c r="E9" s="1">
-        <v>-4.5019195706814538e-08</v>
+        <v>-4.4967711604994202e-08</v>
       </c>
       <c r="F9" s="1">
-        <v>0.0048253727071790259</v>
+        <v>0.0048256123750957374</v>
       </c>
       <c r="G9" s="1">
-        <v>0.0046284327506195414</v>
+        <v>0.0046286761123206111</v>
       </c>
       <c r="H9" s="1">
-        <v>0.0048928664358673761</v>
+        <v>0.0048931055679471668</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0046780752021496315</v>
+        <v>0.0046782410828247059</v>
       </c>
       <c r="J9" s="1">
-        <v>0.007226726874439723</v>
+        <v>0.0072269517747022768</v>
       </c>
       <c r="K9" s="1">
-        <v>0.0046558412922153734</v>
+        <v>0.00465610906391822</v>
       </c>
       <c r="L9" s="1">
-        <v>0.00509969789783285</v>
+        <v>0.0051000191185617862</v>
       </c>
       <c r="M9" s="1">
-        <v>0.00092274110705227366</v>
+        <v>0.00092274103196843401</v>
       </c>
       <c r="N9" s="1">
-        <v>0.00022932376237686913</v>
+        <v>0.00022940715165818519</v>
       </c>
       <c r="O9" s="1">
-        <v>1.3502837975760051e-05</v>
+        <v>1.3617581637646414e-05</v>
       </c>
       <c r="P9" s="1">
-        <v>0.00014823427572651878</v>
+        <v>0.00014831317283312342</v>
       </c>
       <c r="Q9" s="1">
-        <v>-4.9821435197587409e-05</v>
+        <v>-4.9911335056375145e-05</v>
       </c>
       <c r="R9" s="1">
-        <v>6.8138658574725059e-05</v>
+        <v>6.8146988212446709e-05</v>
       </c>
       <c r="S9" s="1">
-        <v>0.00015470808765000475</v>
+        <v>0.00015474426430268082</v>
       </c>
       <c r="T9" s="1">
-        <v>-0.00015890402544557156</v>
+        <v>-0.00015882787563218292</v>
       </c>
       <c r="U9" s="1">
-        <v>-8.6050511071782826e-05</v>
+        <v>-8.5904979097464924e-05</v>
       </c>
       <c r="V9" s="1">
-        <v>1.7383106161056013e-05</v>
+        <v>1.6693889480130092e-05</v>
       </c>
       <c r="W9" s="1">
-        <v>-0.00015127125632723539</v>
+        <v>-0.00015155775785743737</v>
       </c>
       <c r="X9" s="1">
-        <v>0.00077238395248175077</v>
+        <v>0.00077212829655680111</v>
       </c>
       <c r="Y9" s="1">
-        <v>0.0017848622337234277</v>
+        <v>0.0017846865085273432</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.3727905244657005e-05</v>
+        <v>-9.3723654982280771e-05</v>
       </c>
       <c r="AA9" s="1">
-        <v>-3.2864155674861581e-05</v>
+        <v>-3.293249802066605e-05</v>
       </c>
       <c r="AB9" s="1">
-        <v>0.00032457542267697558</v>
+        <v>0.00032461544543753006</v>
       </c>
       <c r="AC9" s="1">
-        <v>-0.00014329153982553435</v>
+        <v>-0.00014311111833606276</v>
       </c>
       <c r="AD9" s="1">
-        <v>-5.533329262149284e-05</v>
+        <v>-5.5184564531761594e-05</v>
       </c>
       <c r="AE9" s="1">
-        <v>-0.0001909090230916104</v>
+        <v>-0.00019088401157985209</v>
       </c>
       <c r="AF9" s="1">
-        <v>-6.2109427909475077e-07</v>
+        <v>-6.2528403432598155e-07</v>
       </c>
       <c r="AG9" s="1">
-        <v>0.00012727632572262244</v>
+        <v>0.00012736446351298801</v>
       </c>
       <c r="AH9" s="1">
-        <v>0.00023812772419591198</v>
+        <v>0.00023814272684841153</v>
       </c>
       <c r="AI9" s="1">
-        <v>-0.0055623260142673454</v>
+        <v>-0.0055623877272562737</v>
       </c>
     </row>
     <row r="10">
@@ -1416,106 +1416,106 @@
         <v>35</v>
       </c>
       <c r="B10" s="1">
-        <v>-0.30729212216146468</v>
+        <v>-0.30728191859251586</v>
       </c>
       <c r="C10" s="1">
-        <v>0.00011517777087979501</v>
+        <v>0.00011519149819323912</v>
       </c>
       <c r="D10" s="1">
-        <v>3.15622655372736e-05</v>
+        <v>3.1558733915692283e-05</v>
       </c>
       <c r="E10" s="1">
-        <v>-2.3780927825340882e-07</v>
+        <v>-2.3777300363348163e-07</v>
       </c>
       <c r="F10" s="1">
-        <v>0.0046703214728683693</v>
+        <v>0.0046705838121677955</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0047571737385850767</v>
+        <v>0.0047574262000728848</v>
       </c>
       <c r="H10" s="1">
-        <v>0.0046295153842094323</v>
+        <v>0.004629777184357955</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0043838530048954652</v>
+        <v>0.0043840760017050708</v>
       </c>
       <c r="J10" s="1">
-        <v>0.0046558412922153734</v>
+        <v>0.00465610906391822</v>
       </c>
       <c r="K10" s="1">
-        <v>0.0052956583297501707</v>
+        <v>0.0052959509293839654</v>
       </c>
       <c r="L10" s="1">
-        <v>0.0050431853142137543</v>
+        <v>0.0050435190084587708</v>
       </c>
       <c r="M10" s="1">
-        <v>0.00019492245761402904</v>
+        <v>0.00019503924863343232</v>
       </c>
       <c r="N10" s="1">
-        <v>-0.00021590277475651374</v>
+        <v>-0.00021580649335912008</v>
       </c>
       <c r="O10" s="1">
-        <v>9.7090395190960774e-05</v>
+        <v>9.7108149070489831e-05</v>
       </c>
       <c r="P10" s="1">
-        <v>0.00017061561339048862</v>
+        <v>0.00017065132226413808</v>
       </c>
       <c r="Q10" s="1">
-        <v>0.00017380052050891071</v>
+        <v>0.0001738790030550324</v>
       </c>
       <c r="R10" s="1">
-        <v>-6.4312963222357307e-05</v>
+        <v>-6.4506007119427642e-05</v>
       </c>
       <c r="S10" s="1">
-        <v>-3.056292950811266e-06</v>
+        <v>-3.3315418922670874e-06</v>
       </c>
       <c r="T10" s="1">
-        <v>-8.4776023901850499e-06</v>
+        <v>-8.6821748405422e-06</v>
       </c>
       <c r="U10" s="1">
-        <v>-0.00026468255006776176</v>
+        <v>-0.00026489161806194901</v>
       </c>
       <c r="V10" s="1">
-        <v>5.7549884443015517e-05</v>
+        <v>5.7860333095574525e-05</v>
       </c>
       <c r="W10" s="1">
-        <v>0.00033514555559514933</v>
+        <v>0.00033546175108599093</v>
       </c>
       <c r="X10" s="1">
-        <v>0.00054880521816930128</v>
+        <v>0.00054912120370216057</v>
       </c>
       <c r="Y10" s="1">
-        <v>0.0013740685193620039</v>
+        <v>0.001374503436026399</v>
       </c>
       <c r="Z10" s="1">
-        <v>-8.8301389782695914e-05</v>
+        <v>-8.8325034545054363e-05</v>
       </c>
       <c r="AA10" s="1">
-        <v>-0.00018935942338966431</v>
+        <v>-0.00018935105215490635</v>
       </c>
       <c r="AB10" s="1">
-        <v>0.00029090483733027177</v>
+        <v>0.00029099613388316233</v>
       </c>
       <c r="AC10" s="1">
-        <v>9.6569270227219416e-05</v>
+        <v>9.6735004546593707e-05</v>
       </c>
       <c r="AD10" s="1">
-        <v>0.00010418293855289455</v>
+        <v>0.0001042264218092853</v>
       </c>
       <c r="AE10" s="1">
-        <v>-2.1851853514240653e-05</v>
+        <v>-2.1788348348834386e-05</v>
       </c>
       <c r="AF10" s="1">
-        <v>-1.242640000420251e-05</v>
+        <v>-1.2440144133851511e-05</v>
       </c>
       <c r="AG10" s="1">
-        <v>0.00032090980639919511</v>
+        <v>0.0003209557824896507</v>
       </c>
       <c r="AH10" s="1">
-        <v>0.00031367030446644776</v>
+        <v>0.00031380229474831426</v>
       </c>
       <c r="AI10" s="1">
-        <v>-0.0058567000249403105</v>
+        <v>-0.0058568792463368404</v>
       </c>
     </row>
     <row r="11">
@@ -1523,106 +1523,106 @@
         <v>36</v>
       </c>
       <c r="B11" s="1">
-        <v>-0.40454236988194797</v>
+        <v>-0.40453107512116421</v>
       </c>
       <c r="C11" s="1">
-        <v>0.00052108024386409162</v>
+        <v>0.00052103688379686881</v>
       </c>
       <c r="D11" s="1">
-        <v>2.1123565515370109e-05</v>
+        <v>2.1125033725385886e-05</v>
       </c>
       <c r="E11" s="1">
-        <v>-1.1604788968772363e-08</v>
+        <v>-1.1614914391957423e-08</v>
       </c>
       <c r="F11" s="1">
-        <v>0.0048721464073992454</v>
+        <v>0.0048725567351219357</v>
       </c>
       <c r="G11" s="1">
-        <v>0.0045825897308364779</v>
+        <v>0.0045829281155009187</v>
       </c>
       <c r="H11" s="1">
-        <v>0.0050716875864671631</v>
+        <v>0.0050719893959313422</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0048788550422076823</v>
+        <v>0.0048791707170408281</v>
       </c>
       <c r="J11" s="1">
-        <v>0.00509969789783285</v>
+        <v>0.0051000191185617862</v>
       </c>
       <c r="K11" s="1">
-        <v>0.0050431853142137543</v>
+        <v>0.0050435190084587708</v>
       </c>
       <c r="L11" s="1">
-        <v>0.010506739835812157</v>
+        <v>0.010507220907839789</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0011145632555974924</v>
+        <v>0.0011147549186213898</v>
       </c>
       <c r="N11" s="1">
-        <v>7.5897423755851273e-05</v>
+        <v>7.606858938081747e-05</v>
       </c>
       <c r="O11" s="1">
-        <v>0.00028679534806909704</v>
+        <v>0.00028683370417673635</v>
       </c>
       <c r="P11" s="1">
-        <v>0.0002797683334658436</v>
+        <v>0.00027985132875303653</v>
       </c>
       <c r="Q11" s="1">
-        <v>0.00017974753799660697</v>
+        <v>0.00017992079646731059</v>
       </c>
       <c r="R11" s="1">
-        <v>7.5195361971890518e-05</v>
+        <v>7.516715790468597e-05</v>
       </c>
       <c r="S11" s="1">
-        <v>5.8943154266170416e-05</v>
+        <v>5.8873582168588758e-05</v>
       </c>
       <c r="T11" s="1">
-        <v>-9.449150627769071e-05</v>
+        <v>-9.4503712716841721e-05</v>
       </c>
       <c r="U11" s="1">
-        <v>0.00010152053614090068</v>
+        <v>0.00010152367348750671</v>
       </c>
       <c r="V11" s="1">
-        <v>7.8096126754415279e-05</v>
+        <v>7.9436968989844963e-05</v>
       </c>
       <c r="W11" s="1">
-        <v>0.00027000144375598592</v>
+        <v>0.00027085417726376167</v>
       </c>
       <c r="X11" s="1">
-        <v>0.00083381817199853451</v>
+        <v>0.00083471801687879537</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.0019770426864075402</v>
+        <v>0.001978097150966863</v>
       </c>
       <c r="Z11" s="1">
-        <v>-0.00029959734920110214</v>
+        <v>-0.00029964542548491018</v>
       </c>
       <c r="AA11" s="1">
-        <v>-9.3359109020845681e-05</v>
+        <v>-9.3307477727147385e-05</v>
       </c>
       <c r="AB11" s="1">
-        <v>0.00023328268872757065</v>
+        <v>0.00023329937459805631</v>
       </c>
       <c r="AC11" s="1">
-        <v>9.996348617431804e-05</v>
+        <v>0.00010007515246141961</v>
       </c>
       <c r="AD11" s="1">
-        <v>6.3570387819939468e-05</v>
+        <v>6.3654548704147586e-05</v>
       </c>
       <c r="AE11" s="1">
-        <v>-0.00021059699516398417</v>
+        <v>-0.00021060086451884781</v>
       </c>
       <c r="AF11" s="1">
-        <v>-2.9573377166804376e-05</v>
+        <v>-2.95887091056339e-05</v>
       </c>
       <c r="AG11" s="1">
-        <v>0.00043169606570728561</v>
+        <v>0.00043162195916210053</v>
       </c>
       <c r="AH11" s="1">
-        <v>0.00033505175870773732</v>
+        <v>0.0003351770764789758</v>
       </c>
       <c r="AI11" s="1">
-        <v>-0.0063754335886697898</v>
+        <v>-0.0063765035273892464</v>
       </c>
     </row>
     <row r="12">
@@ -1630,106 +1630,106 @@
         <v>37</v>
       </c>
       <c r="B12" s="1">
-        <v>0.22796772813521618</v>
+        <v>0.22798500688988635</v>
       </c>
       <c r="C12" s="1">
-        <v>0.00026211477751951511</v>
+        <v>0.00026209919399141545</v>
       </c>
       <c r="D12" s="1">
-        <v>0.00015347794856690878</v>
+        <v>0.00015348692503866002</v>
       </c>
       <c r="E12" s="1">
-        <v>-1.2296513467831838e-06</v>
+        <v>-1.2296955408606344e-06</v>
       </c>
       <c r="F12" s="1">
-        <v>0.00032968851069084651</v>
+        <v>0.00032965518784308287</v>
       </c>
       <c r="G12" s="1">
-        <v>8.9906585172103132e-05</v>
+        <v>8.9897160670459844e-05</v>
       </c>
       <c r="H12" s="1">
-        <v>0.00073491890253591773</v>
+        <v>0.00073492372372894717</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0014106376538499483</v>
+        <v>0.0014105312585434987</v>
       </c>
       <c r="J12" s="1">
-        <v>0.00092274110705227366</v>
+        <v>0.00092274103196843401</v>
       </c>
       <c r="K12" s="1">
-        <v>0.00019492245761402904</v>
+        <v>0.00019503924863343232</v>
       </c>
       <c r="L12" s="1">
-        <v>0.0011145632555974924</v>
+        <v>0.0011147549186213898</v>
       </c>
       <c r="M12" s="1">
-        <v>0.013203209172028914</v>
+        <v>0.013203226628853048</v>
       </c>
       <c r="N12" s="1">
-        <v>0.0025272410614723632</v>
+        <v>0.0025273543496413075</v>
       </c>
       <c r="O12" s="1">
-        <v>-0.0088774289216302215</v>
+        <v>-0.0088773015388522621</v>
       </c>
       <c r="P12" s="1">
-        <v>-0.00015524101211142295</v>
+        <v>-0.00015540311891834016</v>
       </c>
       <c r="Q12" s="1">
-        <v>-0.00045354819923159023</v>
+        <v>-0.00045342894415612662</v>
       </c>
       <c r="R12" s="1">
-        <v>-5.8532171883503552e-05</v>
+        <v>-5.866241636366524e-05</v>
       </c>
       <c r="S12" s="1">
-        <v>-7.0872298656933909e-05</v>
+        <v>-7.1463034194343066e-05</v>
       </c>
       <c r="T12" s="1">
-        <v>-8.4530108489627742e-05</v>
+        <v>-8.4676294461554641e-05</v>
       </c>
       <c r="U12" s="1">
-        <v>-2.4048356489555795e-05</v>
+        <v>-2.417317035463681e-05</v>
       </c>
       <c r="V12" s="1">
-        <v>0.00050168858656815789</v>
+        <v>0.00050056564985480312</v>
       </c>
       <c r="W12" s="1">
-        <v>0.0020222132028897373</v>
+        <v>0.0020218895980936538</v>
       </c>
       <c r="X12" s="1">
-        <v>0.0030236058310321272</v>
+        <v>0.003023360280326578</v>
       </c>
       <c r="Y12" s="1">
-        <v>0.0027733159243299192</v>
+        <v>0.0027730627979547472</v>
       </c>
       <c r="Z12" s="1">
-        <v>-0.00022006258845881193</v>
+        <v>-0.00022006907889646275</v>
       </c>
       <c r="AA12" s="1">
-        <v>3.2586273834562802e-05</v>
+        <v>3.2547988835394817e-05</v>
       </c>
       <c r="AB12" s="1">
-        <v>7.4833452486069724e-05</v>
+        <v>7.5226980097970516e-05</v>
       </c>
       <c r="AC12" s="1">
-        <v>-0.00038415162587905009</v>
+        <v>-0.00038361733544201547</v>
       </c>
       <c r="AD12" s="1">
-        <v>-2.7466781197101146e-06</v>
+        <v>-2.2198173791241021e-06</v>
       </c>
       <c r="AE12" s="1">
-        <v>8.4829266834013893e-05</v>
+        <v>8.5104492900944795e-05</v>
       </c>
       <c r="AF12" s="1">
-        <v>-4.9473496396261083e-06</v>
+        <v>-5.0061487570539289e-06</v>
       </c>
       <c r="AG12" s="1">
-        <v>-0.00038923973069070195</v>
+        <v>-0.00038904825937731424</v>
       </c>
       <c r="AH12" s="1">
-        <v>-0.0002102157684431066</v>
+        <v>-0.00020981183735673003</v>
       </c>
       <c r="AI12" s="1">
-        <v>-0.0071928328451068332</v>
+        <v>-0.0071919325328668147</v>
       </c>
     </row>
     <row r="13">
@@ -1737,106 +1737,106 @@
         <v>38</v>
       </c>
       <c r="B13" s="1">
-        <v>-0.094519338585477369</v>
+        <v>-0.094525742544796426</v>
       </c>
       <c r="C13" s="1">
-        <v>7.5024814481137894e-05</v>
+        <v>7.5076537876437547e-05</v>
       </c>
       <c r="D13" s="1">
-        <v>1.7997351592592372e-05</v>
+        <v>1.7989508519135919e-05</v>
       </c>
       <c r="E13" s="1">
-        <v>-2.4044850694781615e-07</v>
+        <v>-2.4035720670042705e-07</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.00020113653727649432</v>
+        <v>-0.00020111028281137242</v>
       </c>
       <c r="G13" s="1">
-        <v>-1.8724369603991854e-05</v>
+        <v>-1.8639634497153584e-05</v>
       </c>
       <c r="H13" s="1">
-        <v>0.00014224469237861096</v>
+        <v>0.00014228108393574091</v>
       </c>
       <c r="I13" s="1">
-        <v>0.00010525573173797995</v>
+        <v>0.00010529295631741056</v>
       </c>
       <c r="J13" s="1">
-        <v>0.00022932376237686913</v>
+        <v>0.00022940715165818519</v>
       </c>
       <c r="K13" s="1">
-        <v>-0.00021590277475651374</v>
+        <v>-0.00021580649335912008</v>
       </c>
       <c r="L13" s="1">
-        <v>7.5897423755851273e-05</v>
+        <v>7.606858938081747e-05</v>
       </c>
       <c r="M13" s="1">
-        <v>0.0025272410614723632</v>
+        <v>0.0025273543496413075</v>
       </c>
       <c r="N13" s="1">
-        <v>0.0032662501917384906</v>
+        <v>0.0032664084529954976</v>
       </c>
       <c r="O13" s="1">
-        <v>6.5647628928889549e-05</v>
+        <v>6.5655435413573056e-05</v>
       </c>
       <c r="P13" s="1">
-        <v>-0.00010377308648249677</v>
+        <v>-0.00010384018113933564</v>
       </c>
       <c r="Q13" s="1">
-        <v>-0.00034222400602851527</v>
+        <v>-0.00034236749109032411</v>
       </c>
       <c r="R13" s="1">
-        <v>5.9171469970824308e-05</v>
+        <v>5.9209478366918839e-05</v>
       </c>
       <c r="S13" s="1">
-        <v>0.00012183005066459282</v>
+        <v>0.00012182174585149207</v>
       </c>
       <c r="T13" s="1">
-        <v>0.00038129449138779771</v>
+        <v>0.00038132507602456984</v>
       </c>
       <c r="U13" s="1">
-        <v>0.00057174275721078873</v>
+        <v>0.00057177237595289437</v>
       </c>
       <c r="V13" s="1">
-        <v>5.876728893344595e-05</v>
+        <v>5.8078365585781573e-05</v>
       </c>
       <c r="W13" s="1">
-        <v>0.0019142766797069423</v>
+        <v>0.0019140590665750693</v>
       </c>
       <c r="X13" s="1">
-        <v>0.0026582327290862835</v>
+        <v>0.0026580964336028203</v>
       </c>
       <c r="Y13" s="1">
-        <v>0.002591507318392066</v>
+        <v>0.0025913672061562091</v>
       </c>
       <c r="Z13" s="1">
-        <v>-0.00013326417041872827</v>
+        <v>-0.00013326755040911199</v>
       </c>
       <c r="AA13" s="1">
-        <v>2.8569475604282022e-05</v>
+        <v>2.8552233570940089e-05</v>
       </c>
       <c r="AB13" s="1">
-        <v>-5.2887370634620377e-05</v>
+        <v>-5.2827399760034185e-05</v>
       </c>
       <c r="AC13" s="1">
-        <v>-0.00018193685850591322</v>
+        <v>-0.00018187408605579471</v>
       </c>
       <c r="AD13" s="1">
-        <v>-0.00016519126492804285</v>
+        <v>-0.00016504332285276739</v>
       </c>
       <c r="AE13" s="1">
-        <v>-4.9810358773324918e-05</v>
+        <v>-4.9756753791821472e-05</v>
       </c>
       <c r="AF13" s="1">
-        <v>-1.3557596760123148e-05</v>
+        <v>-1.3559413908074817e-05</v>
       </c>
       <c r="AG13" s="1">
-        <v>3.3733079687679399e-05</v>
+        <v>3.3766524974406138e-05</v>
       </c>
       <c r="AH13" s="1">
-        <v>-0.00011222199347195522</v>
+        <v>-0.0001122300233948536</v>
       </c>
       <c r="AI13" s="1">
-        <v>-0.0028232882791438436</v>
+        <v>-0.002823085037399334</v>
       </c>
     </row>
     <row r="14">
@@ -1844,106 +1844,106 @@
         <v>39</v>
       </c>
       <c r="B14" s="1">
-        <v>-0.33506155142049943</v>
+        <v>-0.33506904622237305</v>
       </c>
       <c r="C14" s="1">
-        <v>-0.00014631348433018985</v>
+        <v>-0.00014628448021894189</v>
       </c>
       <c r="D14" s="1">
-        <v>-2.4300747964118004e-05</v>
+        <v>-2.4334805518614811e-05</v>
       </c>
       <c r="E14" s="1">
-        <v>2.5102399187074278e-07</v>
+        <v>2.5134188905756324e-07</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0009304033297670869</v>
+        <v>0.00093052771640258298</v>
       </c>
       <c r="G14" s="1">
-        <v>8.4920763309930555e-05</v>
+        <v>8.4867856535652435e-05</v>
       </c>
       <c r="H14" s="1">
-        <v>-0.00022841115384627392</v>
+        <v>-0.00022839924974783201</v>
       </c>
       <c r="I14" s="1">
-        <v>-0.0001760664255580866</v>
+        <v>-0.00017598884206392865</v>
       </c>
       <c r="J14" s="1">
-        <v>1.3502837975760051e-05</v>
+        <v>1.3617581637646414e-05</v>
       </c>
       <c r="K14" s="1">
-        <v>9.7090395190960774e-05</v>
+        <v>9.7108149070489831e-05</v>
       </c>
       <c r="L14" s="1">
-        <v>0.00028679534806909704</v>
+        <v>0.00028683370417673635</v>
       </c>
       <c r="M14" s="1">
-        <v>-0.0088774289216302215</v>
+        <v>-0.0088773015388522621</v>
       </c>
       <c r="N14" s="1">
-        <v>6.5647628928889549e-05</v>
+        <v>6.5655435413573056e-05</v>
       </c>
       <c r="O14" s="1">
-        <v>0.017834977776912373</v>
+        <v>0.017834904904250493</v>
       </c>
       <c r="P14" s="1">
-        <v>0.0015508889243148007</v>
+        <v>0.0015511286639550525</v>
       </c>
       <c r="Q14" s="1">
-        <v>0.0016783302767853</v>
+        <v>0.0016783802063468553</v>
       </c>
       <c r="R14" s="1">
-        <v>4.6701483532707159e-06</v>
+        <v>4.6493072845316574e-06</v>
       </c>
       <c r="S14" s="1">
-        <v>-4.3469560338120332e-05</v>
+        <v>-4.3242262589291345e-05</v>
       </c>
       <c r="T14" s="1">
-        <v>0.0001966768682806069</v>
+        <v>0.00019656712085782673</v>
       </c>
       <c r="U14" s="1">
-        <v>0.00010343757767997141</v>
+        <v>0.00010327292914708703</v>
       </c>
       <c r="V14" s="1">
-        <v>-0.0002830027116443921</v>
+        <v>-0.00028160738373653079</v>
       </c>
       <c r="W14" s="1">
-        <v>0.00032478638256148485</v>
+        <v>0.0003255555256660961</v>
       </c>
       <c r="X14" s="1">
-        <v>0.00024458338733387655</v>
+        <v>0.00024534701779513709</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.00028025822215264028</v>
+        <v>0.00028108956476705343</v>
       </c>
       <c r="Z14" s="1">
-        <v>9.9586370740198407e-05</v>
+        <v>9.9567745906614351e-05</v>
       </c>
       <c r="AA14" s="1">
-        <v>-0.00025446021819621617</v>
+        <v>-0.00025441639759160372</v>
       </c>
       <c r="AB14" s="1">
-        <v>-0.00046734704395442166</v>
+        <v>-0.00046753039124638698</v>
       </c>
       <c r="AC14" s="1">
-        <v>0.0010045878634789454</v>
+        <v>0.0010042069158438011</v>
       </c>
       <c r="AD14" s="1">
-        <v>-0.00015049816258301391</v>
+        <v>-0.00015093501953635053</v>
       </c>
       <c r="AE14" s="1">
-        <v>-0.00023249580819562955</v>
+        <v>-0.00023270938346594213</v>
       </c>
       <c r="AF14" s="1">
-        <v>6.2950663784039872e-06</v>
+        <v>6.3361311039926405e-06</v>
       </c>
       <c r="AG14" s="1">
-        <v>-6.6477564774155076e-05</v>
+        <v>-6.6587311333537839e-05</v>
       </c>
       <c r="AH14" s="1">
-        <v>0.00027228498052549481</v>
+        <v>0.00027206934423810124</v>
       </c>
       <c r="AI14" s="1">
-        <v>-0.0010319212385375008</v>
+        <v>-0.0010325015778257412</v>
       </c>
     </row>
     <row r="15">
@@ -1951,106 +1951,106 @@
         <v>40</v>
       </c>
       <c r="B15" s="1">
-        <v>-0.11111192386728244</v>
+        <v>-0.11113423490377686</v>
       </c>
       <c r="C15" s="1">
-        <v>-0.0001504226716678639</v>
+        <v>-0.00015036823599548759</v>
       </c>
       <c r="D15" s="1">
-        <v>-3.2200531772687486e-05</v>
+        <v>-3.2218804070045771e-05</v>
       </c>
       <c r="E15" s="1">
-        <v>3.0893369107711901e-07</v>
+        <v>3.0910166094041475e-07</v>
       </c>
       <c r="F15" s="1">
-        <v>0.00063368203544821164</v>
+        <v>0.00063374456441793719</v>
       </c>
       <c r="G15" s="1">
-        <v>8.7234997166764795e-05</v>
+        <v>8.7168953832682857e-05</v>
       </c>
       <c r="H15" s="1">
-        <v>-0.0001746491289784549</v>
+        <v>-0.00017463863299571267</v>
       </c>
       <c r="I15" s="1">
-        <v>-0.00029686071200720702</v>
+        <v>-0.00029689086097268872</v>
       </c>
       <c r="J15" s="1">
-        <v>0.00014823427572651878</v>
+        <v>0.00014831317283312342</v>
       </c>
       <c r="K15" s="1">
-        <v>0.00017061561339048862</v>
+        <v>0.00017065132226413808</v>
       </c>
       <c r="L15" s="1">
-        <v>0.0002797683334658436</v>
+        <v>0.00027985132875303653</v>
       </c>
       <c r="M15" s="1">
-        <v>-0.00015524101211142295</v>
+        <v>-0.00015540311891834016</v>
       </c>
       <c r="N15" s="1">
-        <v>-0.00010377308648249677</v>
+        <v>-0.00010384018113933564</v>
       </c>
       <c r="O15" s="1">
-        <v>0.0015508889243148007</v>
+        <v>0.0015511286639550525</v>
       </c>
       <c r="P15" s="1">
-        <v>0.0018947467078142405</v>
+        <v>0.0018949204007421947</v>
       </c>
       <c r="Q15" s="1">
-        <v>0.0015226288579186704</v>
+        <v>0.0015227540488751746</v>
       </c>
       <c r="R15" s="1">
-        <v>-3.2329751659738624e-05</v>
+        <v>-3.2193570426995103e-05</v>
       </c>
       <c r="S15" s="1">
-        <v>1.15312551334826e-05</v>
+        <v>1.1672822190808349e-05</v>
       </c>
       <c r="T15" s="1">
-        <v>9.4980347925547167e-05</v>
+        <v>9.4997798751615833e-05</v>
       </c>
       <c r="U15" s="1">
-        <v>-0.00032089440183834353</v>
+        <v>-0.00032091727769375329</v>
       </c>
       <c r="V15" s="1">
-        <v>-7.6438805474986666e-05</v>
+        <v>-7.6741186139512321e-05</v>
       </c>
       <c r="W15" s="1">
-        <v>-7.9515155160856548e-05</v>
+        <v>-7.9667070001633296e-05</v>
       </c>
       <c r="X15" s="1">
-        <v>0.00014868951782996543</v>
+        <v>0.00014852790007717758</v>
       </c>
       <c r="Y15" s="1">
-        <v>0.00019579031755848726</v>
+        <v>0.0001956804226815169</v>
       </c>
       <c r="Z15" s="1">
-        <v>3.2771132055161784e-05</v>
+        <v>3.2782889101071736e-05</v>
       </c>
       <c r="AA15" s="1">
-        <v>-0.00015133954198028499</v>
+        <v>-0.00015138500222011664</v>
       </c>
       <c r="AB15" s="1">
-        <v>-9.5606798937157892e-05</v>
+        <v>-9.5600249300901909e-05</v>
       </c>
       <c r="AC15" s="1">
-        <v>4.4696501391709286e-05</v>
+        <v>4.4662224686543568e-05</v>
       </c>
       <c r="AD15" s="1">
-        <v>4.2202548481914394e-05</v>
+        <v>4.2043649106421327e-05</v>
       </c>
       <c r="AE15" s="1">
-        <v>9.1416859703396776e-05</v>
+        <v>9.1349858866628813e-05</v>
       </c>
       <c r="AF15" s="1">
-        <v>-9.2170658087262832e-06</v>
+        <v>-9.198748865140623e-06</v>
       </c>
       <c r="AG15" s="1">
-        <v>-0.00033822251339411672</v>
+        <v>-0.00033817467731770984</v>
       </c>
       <c r="AH15" s="1">
-        <v>0.00031142654573763912</v>
+        <v>0.00031137055542476808</v>
       </c>
       <c r="AI15" s="1">
-        <v>-0.00058954971789620557</v>
+        <v>-0.00058943563110173828</v>
       </c>
     </row>
     <row r="16">
@@ -2058,106 +2058,106 @@
         <v>41</v>
       </c>
       <c r="B16" s="1">
-        <v>-0.19158184308024595</v>
+        <v>-0.19151635018256655</v>
       </c>
       <c r="C16" s="1">
-        <v>1.7240655321596647e-05</v>
+        <v>1.7348881433997768e-05</v>
       </c>
       <c r="D16" s="1">
-        <v>-1.2529695370788675e-05</v>
+        <v>-1.2558686222294182e-05</v>
       </c>
       <c r="E16" s="1">
-        <v>3.4984838443742284e-08</v>
+        <v>3.533200603852238e-08</v>
       </c>
       <c r="F16" s="1">
-        <v>0.00037745976610460046</v>
+        <v>0.00037753649611796695</v>
       </c>
       <c r="G16" s="1">
-        <v>0.00023429618317245371</v>
+        <v>0.00023407842635696121</v>
       </c>
       <c r="H16" s="1">
-        <v>-0.00019666709986702348</v>
+        <v>-0.00019673234002288357</v>
       </c>
       <c r="I16" s="1">
-        <v>-0.00024166527585912619</v>
+        <v>-0.00024166471060033893</v>
       </c>
       <c r="J16" s="1">
-        <v>-4.9821435197587409e-05</v>
+        <v>-4.9911335056375145e-05</v>
       </c>
       <c r="K16" s="1">
-        <v>0.00017380052050891071</v>
+        <v>0.0001738790030550324</v>
       </c>
       <c r="L16" s="1">
-        <v>0.00017974753799660697</v>
+        <v>0.00017992079646731059</v>
       </c>
       <c r="M16" s="1">
-        <v>-0.00045354819923159023</v>
+        <v>-0.00045342894415612662</v>
       </c>
       <c r="N16" s="1">
-        <v>-0.00034222400602851527</v>
+        <v>-0.00034236749109032411</v>
       </c>
       <c r="O16" s="1">
-        <v>0.0016783302767853</v>
+        <v>0.0016783802063468553</v>
       </c>
       <c r="P16" s="1">
-        <v>0.0015226288579186704</v>
+        <v>0.0015227540488751746</v>
       </c>
       <c r="Q16" s="1">
-        <v>0.0026193117801309633</v>
+        <v>0.0026195702130443511</v>
       </c>
       <c r="R16" s="1">
-        <v>0.00015870099195822043</v>
+        <v>0.00015806144942545912</v>
       </c>
       <c r="S16" s="1">
-        <v>0.00022304477110456612</v>
+        <v>0.00022243820192033103</v>
       </c>
       <c r="T16" s="1">
-        <v>0.00044838488528272844</v>
+        <v>0.00044779614334722751</v>
       </c>
       <c r="U16" s="1">
-        <v>4.5905567042535053e-06</v>
+        <v>3.9500486393093375e-06</v>
       </c>
       <c r="V16" s="1">
-        <v>0.0001406597734357626</v>
+        <v>0.00014317038540778265</v>
       </c>
       <c r="W16" s="1">
-        <v>0.00014837995345113415</v>
+        <v>0.00014989976797887558</v>
       </c>
       <c r="X16" s="1">
-        <v>0.00017785419268018596</v>
+        <v>0.00017933967668695683</v>
       </c>
       <c r="Y16" s="1">
-        <v>0.00027754921601432945</v>
+        <v>0.0002790754528439127</v>
       </c>
       <c r="Z16" s="1">
-        <v>3.0771138346440715e-05</v>
+        <v>3.0721731431154108e-05</v>
       </c>
       <c r="AA16" s="1">
-        <v>-0.00015626837671342436</v>
+        <v>-0.00015617379926339181</v>
       </c>
       <c r="AB16" s="1">
-        <v>-0.00051156819443302112</v>
+        <v>-0.00051157164252362605</v>
       </c>
       <c r="AC16" s="1">
-        <v>-3.1283870040078616e-06</v>
+        <v>-3.2260322206749664e-06</v>
       </c>
       <c r="AD16" s="1">
-        <v>-0.00010253632380451705</v>
+        <v>-0.00010253843728468624</v>
       </c>
       <c r="AE16" s="1">
-        <v>0.00010867499151273315</v>
+        <v>0.00010865995116393103</v>
       </c>
       <c r="AF16" s="1">
-        <v>1.4215581820925611e-05</v>
+        <v>1.420966022217161e-05</v>
       </c>
       <c r="AG16" s="1">
-        <v>-0.00033315234725321812</v>
+        <v>-0.00033350677976503153</v>
       </c>
       <c r="AH16" s="1">
-        <v>0.00024117536479581746</v>
+        <v>0.00024130411421126405</v>
       </c>
       <c r="AI16" s="1">
-        <v>-0.0014858645671962465</v>
+        <v>-0.0014862610977400322</v>
       </c>
     </row>
     <row r="17">
@@ -2165,106 +2165,106 @@
         <v>42</v>
       </c>
       <c r="B17" s="1">
-        <v>0.085046671350578057</v>
+        <v>0.0849724736461651</v>
       </c>
       <c r="C17" s="1">
-        <v>-0.00011910932376519269</v>
+        <v>-0.00011910365070319105</v>
       </c>
       <c r="D17" s="1">
-        <v>-3.7453550226100178e-05</v>
+        <v>-3.7458337694319942e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>3.6595427758275255e-07</v>
+        <v>3.6597968877485047e-07</v>
       </c>
       <c r="F17" s="1">
-        <v>1.6870920753296733e-05</v>
+        <v>1.6826716591518062e-05</v>
       </c>
       <c r="G17" s="1">
-        <v>0.00019790487078574759</v>
+        <v>0.00019817852710917784</v>
       </c>
       <c r="H17" s="1">
-        <v>7.9129888550110274e-05</v>
+        <v>7.8888135405267125e-05</v>
       </c>
       <c r="I17" s="1">
-        <v>2.1342656319985054e-05</v>
+        <v>2.1079921182893657e-05</v>
       </c>
       <c r="J17" s="1">
-        <v>6.8138658574725059e-05</v>
+        <v>6.8146988212446709e-05</v>
       </c>
       <c r="K17" s="1">
-        <v>-6.4312963222357307e-05</v>
+        <v>-6.4506007119427642e-05</v>
       </c>
       <c r="L17" s="1">
-        <v>7.5195361971890518e-05</v>
+        <v>7.516715790468597e-05</v>
       </c>
       <c r="M17" s="1">
-        <v>-5.8532171883503552e-05</v>
+        <v>-5.866241636366524e-05</v>
       </c>
       <c r="N17" s="1">
-        <v>5.9171469970824308e-05</v>
+        <v>5.9209478366918839e-05</v>
       </c>
       <c r="O17" s="1">
-        <v>4.6701483532707159e-06</v>
+        <v>4.6493072845316574e-06</v>
       </c>
       <c r="P17" s="1">
-        <v>-3.2329751659738624e-05</v>
+        <v>-3.2193570426995103e-05</v>
       </c>
       <c r="Q17" s="1">
-        <v>0.00015870099195822043</v>
+        <v>0.00015806144942545912</v>
       </c>
       <c r="R17" s="1">
-        <v>0.0065840532661240606</v>
+        <v>0.0065826433487436537</v>
       </c>
       <c r="S17" s="1">
-        <v>0.0058663626174930419</v>
+        <v>0.0058649417361572023</v>
       </c>
       <c r="T17" s="1">
-        <v>0.0058604056136178327</v>
+        <v>0.0058589257271120894</v>
       </c>
       <c r="U17" s="1">
-        <v>0.0058331702566612846</v>
+        <v>0.0058316238515196605</v>
       </c>
       <c r="V17" s="1">
-        <v>-9.0427723659067911e-05</v>
+        <v>-9.2809419649203312e-05</v>
       </c>
       <c r="W17" s="1">
-        <v>9.0440026809771859e-05</v>
+        <v>8.8905473932556845e-05</v>
       </c>
       <c r="X17" s="1">
-        <v>9.3871743006484283e-05</v>
+        <v>9.2483619022864843e-05</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.00011091060839970874</v>
+        <v>0.00010938392672230242</v>
       </c>
       <c r="Z17" s="1">
-        <v>-4.706742944154339e-05</v>
+        <v>-4.7014779429000136e-05</v>
       </c>
       <c r="AA17" s="1">
-        <v>7.6719584510547109e-05</v>
+        <v>7.6648640624824797e-05</v>
       </c>
       <c r="AB17" s="1">
-        <v>-0.00021215051267309878</v>
+        <v>-0.00021243013952527371</v>
       </c>
       <c r="AC17" s="1">
-        <v>-1.8808264159679306e-05</v>
+        <v>-1.892949475234499e-05</v>
       </c>
       <c r="AD17" s="1">
-        <v>4.324738019545902e-06</v>
+        <v>4.4386814656974846e-06</v>
       </c>
       <c r="AE17" s="1">
-        <v>3.5392185713120205e-05</v>
+        <v>3.5193778356397117e-05</v>
       </c>
       <c r="AF17" s="1">
-        <v>1.2714178479155433e-05</v>
+        <v>1.2696943429794656e-05</v>
       </c>
       <c r="AG17" s="1">
-        <v>-8.8888418991317844e-05</v>
+        <v>-8.9811991759721627e-05</v>
       </c>
       <c r="AH17" s="1">
-        <v>-7.1954808626651257e-05</v>
+        <v>-7.1998494195376662e-05</v>
       </c>
       <c r="AI17" s="1">
-        <v>-0.005212041490429576</v>
+        <v>-0.0052084841819524403</v>
       </c>
     </row>
     <row r="18">
@@ -2272,106 +2272,106 @@
         <v>43</v>
       </c>
       <c r="B18" s="1">
-        <v>0.1907009619341887</v>
+        <v>0.1905337256879647</v>
       </c>
       <c r="C18" s="1">
-        <v>-0.00011571601765513991</v>
+        <v>-0.00011556486340071542</v>
       </c>
       <c r="D18" s="1">
-        <v>-6.4163424380623933e-05</v>
+        <v>-6.4187775410812898e-05</v>
       </c>
       <c r="E18" s="1">
-        <v>6.743524837525216e-07</v>
+        <v>6.7452758240166234e-07</v>
       </c>
       <c r="F18" s="1">
-        <v>-6.6851619706022217e-06</v>
+        <v>-6.9205031003239281e-06</v>
       </c>
       <c r="G18" s="1">
-        <v>9.0251582091518636e-05</v>
+        <v>9.0550624057554987e-05</v>
       </c>
       <c r="H18" s="1">
-        <v>4.7007695912139227e-05</v>
+        <v>4.6738658598921302e-05</v>
       </c>
       <c r="I18" s="1">
-        <v>8.6067423509884119e-05</v>
+        <v>8.5677321705828629e-05</v>
       </c>
       <c r="J18" s="1">
-        <v>0.00015470808765000475</v>
+        <v>0.00015474426430268082</v>
       </c>
       <c r="K18" s="1">
-        <v>-3.056292950811266e-06</v>
+        <v>-3.3315418922670874e-06</v>
       </c>
       <c r="L18" s="1">
-        <v>5.8943154266170416e-05</v>
+        <v>5.8873582168588758e-05</v>
       </c>
       <c r="M18" s="1">
-        <v>-7.0872298656933909e-05</v>
+        <v>-7.1463034194343066e-05</v>
       </c>
       <c r="N18" s="1">
-        <v>0.00012183005066459282</v>
+        <v>0.00012182174585149207</v>
       </c>
       <c r="O18" s="1">
-        <v>-4.3469560338120332e-05</v>
+        <v>-4.3242262589291345e-05</v>
       </c>
       <c r="P18" s="1">
-        <v>1.15312551334826e-05</v>
+        <v>1.1672822190808349e-05</v>
       </c>
       <c r="Q18" s="1">
-        <v>0.00022304477110456612</v>
+        <v>0.00022243820192033103</v>
       </c>
       <c r="R18" s="1">
-        <v>0.0058663626174930419</v>
+        <v>0.0058649417361572023</v>
       </c>
       <c r="S18" s="1">
-        <v>0.006824120708963659</v>
+        <v>0.0068230197030526652</v>
       </c>
       <c r="T18" s="1">
-        <v>0.0062544962790954048</v>
+        <v>0.0062531345513367927</v>
       </c>
       <c r="U18" s="1">
-        <v>0.0061170047155011831</v>
+        <v>0.0061155600785897752</v>
       </c>
       <c r="V18" s="1">
-        <v>-0.00024067302468433146</v>
+        <v>-0.00024357340217713705</v>
       </c>
       <c r="W18" s="1">
-        <v>-7.29068319772915e-06</v>
+        <v>-9.2838851698312172e-06</v>
       </c>
       <c r="X18" s="1">
-        <v>-5.6079343857187844e-07</v>
+        <v>-2.4284619037270297e-06</v>
       </c>
       <c r="Y18" s="1">
-        <v>1.6110739907131827e-06</v>
+        <v>-3.8578012009037044e-07</v>
       </c>
       <c r="Z18" s="1">
-        <v>-3.4565882891118252e-05</v>
+        <v>-3.4490693020475184e-05</v>
       </c>
       <c r="AA18" s="1">
-        <v>7.06083323108789e-05</v>
+        <v>7.0468009777775666e-05</v>
       </c>
       <c r="AB18" s="1">
-        <v>-2.6508417137219905e-05</v>
+        <v>-2.655963142805199e-05</v>
       </c>
       <c r="AC18" s="1">
-        <v>-9.3521426413956717e-05</v>
+        <v>-9.3435530137901679e-05</v>
       </c>
       <c r="AD18" s="1">
-        <v>-8.9532176432434427e-05</v>
+        <v>-8.9403800585542736e-05</v>
       </c>
       <c r="AE18" s="1">
-        <v>3.3010360078103169e-05</v>
+        <v>3.305640638191689e-05</v>
       </c>
       <c r="AF18" s="1">
-        <v>-5.4679806765953708e-06</v>
+        <v>-5.4652450479372532e-06</v>
       </c>
       <c r="AG18" s="1">
-        <v>0.00052095509195258273</v>
+        <v>0.00052060695751364461</v>
       </c>
       <c r="AH18" s="1">
-        <v>-6.9498053543663946e-05</v>
+        <v>-6.9761108534720055e-05</v>
       </c>
       <c r="AI18" s="1">
-        <v>-0.0048242525906864349</v>
+        <v>-0.0048203828815311846</v>
       </c>
     </row>
     <row r="19">
@@ -2379,106 +2379,106 @@
         <v>44</v>
       </c>
       <c r="B19" s="1">
-        <v>0.13648914409695237</v>
+        <v>0.13642407788676633</v>
       </c>
       <c r="C19" s="1">
-        <v>-4.4243441594144758e-05</v>
+        <v>-4.4150971816155586e-05</v>
       </c>
       <c r="D19" s="1">
-        <v>-3.6155691423951475e-05</v>
+        <v>-3.6167407837847635e-05</v>
       </c>
       <c r="E19" s="1">
-        <v>4.6072195654517022e-07</v>
+        <v>4.608174562541542e-07</v>
       </c>
       <c r="F19" s="1">
-        <v>-1.7928582155086678e-06</v>
+        <v>-1.9980754949638132e-06</v>
       </c>
       <c r="G19" s="1">
-        <v>0.00010935153787801469</v>
+        <v>0.00010963545907553195</v>
       </c>
       <c r="H19" s="1">
-        <v>-9.9721893548893015e-05</v>
+        <v>-9.9915069139753826e-05</v>
       </c>
       <c r="I19" s="1">
-        <v>7.1910875513445821e-05</v>
+        <v>7.1637821218662563e-05</v>
       </c>
       <c r="J19" s="1">
-        <v>-0.00015890402544557156</v>
+        <v>-0.00015882787563218292</v>
       </c>
       <c r="K19" s="1">
-        <v>-8.4776023901850499e-06</v>
+        <v>-8.6821748405422e-06</v>
       </c>
       <c r="L19" s="1">
-        <v>-9.449150627769071e-05</v>
+        <v>-9.4503712716841721e-05</v>
       </c>
       <c r="M19" s="1">
-        <v>-8.4530108489627742e-05</v>
+        <v>-8.4676294461554641e-05</v>
       </c>
       <c r="N19" s="1">
-        <v>0.00038129449138779771</v>
+        <v>0.00038132507602456984</v>
       </c>
       <c r="O19" s="1">
-        <v>0.0001966768682806069</v>
+        <v>0.00019656712085782673</v>
       </c>
       <c r="P19" s="1">
-        <v>9.4980347925547167e-05</v>
+        <v>9.4997798751615833e-05</v>
       </c>
       <c r="Q19" s="1">
-        <v>0.00044838488528272844</v>
+        <v>0.00044779614334722751</v>
       </c>
       <c r="R19" s="1">
-        <v>0.0058604056136178327</v>
+        <v>0.0058589257271120894</v>
       </c>
       <c r="S19" s="1">
-        <v>0.0062544962790954048</v>
+        <v>0.0062531345513367927</v>
       </c>
       <c r="T19" s="1">
-        <v>0.007053359383790289</v>
+        <v>0.0070519906833675147</v>
       </c>
       <c r="U19" s="1">
-        <v>0.0064918231544090878</v>
+        <v>0.006490356352776578</v>
       </c>
       <c r="V19" s="1">
-        <v>-0.0001120461804928548</v>
+        <v>-0.00011443205458476491</v>
       </c>
       <c r="W19" s="1">
-        <v>0.0001290856868992594</v>
+        <v>0.00012755148381044727</v>
       </c>
       <c r="X19" s="1">
-        <v>9.4746285503453633e-05</v>
+        <v>9.331877445525053e-05</v>
       </c>
       <c r="Y19" s="1">
-        <v>5.9141016341421673e-06</v>
+        <v>4.3895071609525993e-06</v>
       </c>
       <c r="Z19" s="1">
-        <v>-1.415044953726423e-05</v>
+        <v>-1.4100512438041345e-05</v>
       </c>
       <c r="AA19" s="1">
-        <v>1.874010255916163e-05</v>
+        <v>1.8680091532220799e-05</v>
       </c>
       <c r="AB19" s="1">
-        <v>-0.00020892601191444156</v>
+        <v>-0.00020916221684381866</v>
       </c>
       <c r="AC19" s="1">
-        <v>1.3071063921402809e-05</v>
+        <v>1.2953436054778666e-05</v>
       </c>
       <c r="AD19" s="1">
-        <v>-3.6489378424410456e-05</v>
+        <v>-3.6340200214661711e-05</v>
       </c>
       <c r="AE19" s="1">
-        <v>0.00021761130409639427</v>
+        <v>0.00021765638484483492</v>
       </c>
       <c r="AF19" s="1">
-        <v>-1.2262030127587788e-05</v>
+        <v>-1.2271406114615303e-05</v>
       </c>
       <c r="AG19" s="1">
-        <v>0.00029097501126850063</v>
+        <v>0.00029037738598188152</v>
       </c>
       <c r="AH19" s="1">
-        <v>-0.00010224675944311805</v>
+        <v>-0.00010236842477145567</v>
       </c>
       <c r="AI19" s="1">
-        <v>-0.0060099414587628259</v>
+        <v>-0.0060065140391262085</v>
       </c>
     </row>
     <row r="20">
@@ -2486,106 +2486,106 @@
         <v>45</v>
       </c>
       <c r="B20" s="1">
-        <v>0.094375441456469672</v>
+        <v>0.094310088955926283</v>
       </c>
       <c r="C20" s="1">
-        <v>-0.00013956468224718914</v>
+        <v>-0.00013951098953446324</v>
       </c>
       <c r="D20" s="1">
-        <v>4.6209794408663706e-05</v>
+        <v>4.6199514972125296e-05</v>
       </c>
       <c r="E20" s="1">
-        <v>-1.9020991839300092e-07</v>
+        <v>-1.9013421465907751e-07</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.00048788255669139115</v>
+        <v>-0.00048802717102153659</v>
       </c>
       <c r="G20" s="1">
-        <v>-1.9141193785483183e-05</v>
+        <v>-1.8883731247236295e-05</v>
       </c>
       <c r="H20" s="1">
-        <v>0.00052111786338064235</v>
+        <v>0.00052088613542927188</v>
       </c>
       <c r="I20" s="1">
-        <v>0.00022486736374569905</v>
+        <v>0.00022466256521953831</v>
       </c>
       <c r="J20" s="1">
-        <v>-8.6050511071782826e-05</v>
+        <v>-8.5904979097464924e-05</v>
       </c>
       <c r="K20" s="1">
-        <v>-0.00026468255006776176</v>
+        <v>-0.00026489161806194901</v>
       </c>
       <c r="L20" s="1">
-        <v>0.00010152053614090068</v>
+        <v>0.00010152367348750671</v>
       </c>
       <c r="M20" s="1">
-        <v>-2.4048356489555795e-05</v>
+        <v>-2.417317035463681e-05</v>
       </c>
       <c r="N20" s="1">
-        <v>0.00057174275721078873</v>
+        <v>0.00057177237595289437</v>
       </c>
       <c r="O20" s="1">
-        <v>0.00010343757767997141</v>
+        <v>0.00010327292914708703</v>
       </c>
       <c r="P20" s="1">
-        <v>-0.00032089440183834353</v>
+        <v>-0.00032091727769375329</v>
       </c>
       <c r="Q20" s="1">
-        <v>4.5905567042535053e-06</v>
+        <v>3.9500486393093375e-06</v>
       </c>
       <c r="R20" s="1">
-        <v>0.0058331702566612846</v>
+        <v>0.0058316238515196605</v>
       </c>
       <c r="S20" s="1">
-        <v>0.0061170047155011831</v>
+        <v>0.0061155600785897752</v>
       </c>
       <c r="T20" s="1">
-        <v>0.0064918231544090878</v>
+        <v>0.006490356352776578</v>
       </c>
       <c r="U20" s="1">
-        <v>0.0087414147902899544</v>
+        <v>0.0087398127842168265</v>
       </c>
       <c r="V20" s="1">
-        <v>-0.00011446573944092083</v>
+        <v>-0.00011686863597179433</v>
       </c>
       <c r="W20" s="1">
-        <v>0.0001110162832364133</v>
+        <v>0.00010946766114039311</v>
       </c>
       <c r="X20" s="1">
-        <v>7.2604863845638994e-05</v>
+        <v>7.118847575657202e-05</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.00044867180215855083</v>
+        <v>0.00044714402608699196</v>
       </c>
       <c r="Z20" s="1">
-        <v>-4.3680206441036834e-05</v>
+        <v>-4.363070286970798e-05</v>
       </c>
       <c r="AA20" s="1">
-        <v>0.00016252701259978611</v>
+        <v>0.0001624547930171704</v>
       </c>
       <c r="AB20" s="1">
-        <v>5.8449844738702947e-05</v>
+        <v>5.8043301962052395e-05</v>
       </c>
       <c r="AC20" s="1">
-        <v>-8.7928939257170442e-05</v>
+        <v>-8.7989812938883e-05</v>
       </c>
       <c r="AD20" s="1">
-        <v>-0.0001091055841504554</v>
+        <v>-0.00010889695296658299</v>
       </c>
       <c r="AE20" s="1">
-        <v>0.00010065081723502215</v>
+        <v>0.00010066704517814945</v>
       </c>
       <c r="AF20" s="1">
-        <v>1.878946900336399e-05</v>
+        <v>1.8783416111344898e-05</v>
       </c>
       <c r="AG20" s="1">
-        <v>0.00081544827374738227</v>
+        <v>0.00081445922192247347</v>
       </c>
       <c r="AH20" s="1">
-        <v>-0.00029557417715979622</v>
+        <v>-0.00029573213842744046</v>
       </c>
       <c r="AI20" s="1">
-        <v>-0.0085468179151101283</v>
+        <v>-0.0085432583502900103</v>
       </c>
     </row>
     <row r="21">
@@ -2593,106 +2593,106 @@
         <v>46</v>
       </c>
       <c r="B21" s="1">
-        <v>0.1205834748212283</v>
+        <v>0.12084510124167516</v>
       </c>
       <c r="C21" s="1">
-        <v>1.9425490343522579e-05</v>
+        <v>2.0266321623504547e-05</v>
       </c>
       <c r="D21" s="1">
-        <v>1.9751837622613978e-05</v>
+        <v>1.9601045053726636e-05</v>
       </c>
       <c r="E21" s="1">
-        <v>-1.761401030226397e-07</v>
+        <v>-1.7467584370420078e-07</v>
       </c>
       <c r="F21" s="1">
-        <v>6.9706558135713536e-05</v>
+        <v>6.9283174307708086e-05</v>
       </c>
       <c r="G21" s="1">
-        <v>2.1074563161249562e-05</v>
+        <v>2.2699021009721571e-05</v>
       </c>
       <c r="H21" s="1">
-        <v>6.3704198917015928e-05</v>
+        <v>6.4363720871313441e-05</v>
       </c>
       <c r="I21" s="1">
-        <v>0.0001614831541827316</v>
+        <v>0.00016186809643131499</v>
       </c>
       <c r="J21" s="1">
-        <v>1.7383106161056013e-05</v>
+        <v>1.6693889480130092e-05</v>
       </c>
       <c r="K21" s="1">
-        <v>5.7549884443015517e-05</v>
+        <v>5.7860333095574525e-05</v>
       </c>
       <c r="L21" s="1">
-        <v>7.8096126754415279e-05</v>
+        <v>7.9436968989844963e-05</v>
       </c>
       <c r="M21" s="1">
-        <v>0.00050168858656815789</v>
+        <v>0.00050056564985480312</v>
       </c>
       <c r="N21" s="1">
-        <v>5.876728893344595e-05</v>
+        <v>5.8078365585781573e-05</v>
       </c>
       <c r="O21" s="1">
-        <v>-0.0002830027116443921</v>
+        <v>-0.00028160738373653079</v>
       </c>
       <c r="P21" s="1">
-        <v>-7.6438805474986666e-05</v>
+        <v>-7.6741186139512321e-05</v>
       </c>
       <c r="Q21" s="1">
-        <v>0.0001406597734357626</v>
+        <v>0.00014317038540778265</v>
       </c>
       <c r="R21" s="1">
-        <v>-9.0427723659067911e-05</v>
+        <v>-9.2809419649203312e-05</v>
       </c>
       <c r="S21" s="1">
-        <v>-0.00024067302468433146</v>
+        <v>-0.00024357340217713705</v>
       </c>
       <c r="T21" s="1">
-        <v>-0.0001120461804928548</v>
+        <v>-0.00011443205458476491</v>
       </c>
       <c r="U21" s="1">
-        <v>-0.00011446573944092083</v>
+        <v>-0.00011686863597179433</v>
       </c>
       <c r="V21" s="1">
-        <v>0.0016480106487601251</v>
+        <v>0.0016488930180832706</v>
       </c>
       <c r="W21" s="1">
-        <v>0.0010202887775112373</v>
+        <v>0.0010210796668203813</v>
       </c>
       <c r="X21" s="1">
-        <v>0.0010237795169709008</v>
+        <v>0.0010247818547826574</v>
       </c>
       <c r="Y21" s="1">
-        <v>0.001044928469257808</v>
+        <v>0.001046175092324503</v>
       </c>
       <c r="Z21" s="1">
-        <v>-4.3537476979998616e-05</v>
+        <v>-4.365518929645886e-05</v>
       </c>
       <c r="AA21" s="1">
-        <v>7.4921596938549125e-05</v>
+        <v>7.5628287774842599e-05</v>
       </c>
       <c r="AB21" s="1">
-        <v>-0.00025310321532276994</v>
+        <v>-0.00025161792545769376</v>
       </c>
       <c r="AC21" s="1">
-        <v>-0.0002182420867960467</v>
+        <v>-0.00021547988097651881</v>
       </c>
       <c r="AD21" s="1">
-        <v>-4.703608763296229e-05</v>
+        <v>-4.4679485724224246e-05</v>
       </c>
       <c r="AE21" s="1">
-        <v>3.0517426843605254e-05</v>
+        <v>3.2047790430182299e-05</v>
       </c>
       <c r="AF21" s="1">
-        <v>-2.510252179523074e-06</v>
+        <v>-2.595681288296738e-06</v>
       </c>
       <c r="AG21" s="1">
-        <v>-0.00030434473930856859</v>
+        <v>-0.00030505296664115459</v>
       </c>
       <c r="AH21" s="1">
-        <v>1.9414487051385159e-06</v>
+        <v>2.3004398925098439e-06</v>
       </c>
       <c r="AI21" s="1">
-        <v>-0.0012639579208041389</v>
+        <v>-0.0012597753793565621</v>
       </c>
     </row>
     <row r="22">
@@ -2700,106 +2700,106 @@
         <v>47</v>
       </c>
       <c r="B22" s="1">
-        <v>-0.040756496550335551</v>
+        <v>-0.040573152890452657</v>
       </c>
       <c r="C22" s="1">
-        <v>8.5813084666958733e-05</v>
+        <v>8.6222217475913961e-05</v>
       </c>
       <c r="D22" s="1">
-        <v>-2.8904253519728627e-05</v>
+        <v>-2.8975039892373462e-05</v>
       </c>
       <c r="E22" s="1">
-        <v>2.9374673972222272e-07</v>
+        <v>2.9444189595068111e-07</v>
       </c>
       <c r="F22" s="1">
-        <v>9.0411189599724903e-05</v>
+        <v>9.0355876388349774e-05</v>
       </c>
       <c r="G22" s="1">
-        <v>0.00024558685069701956</v>
+        <v>0.00024646928154228095</v>
       </c>
       <c r="H22" s="1">
-        <v>6.7547684784843246e-05</v>
+        <v>6.7937465402927361e-05</v>
       </c>
       <c r="I22" s="1">
-        <v>5.1026576590597773e-05</v>
+        <v>5.1314993713701389e-05</v>
       </c>
       <c r="J22" s="1">
-        <v>-0.00015127125632723539</v>
+        <v>-0.00015155775785743737</v>
       </c>
       <c r="K22" s="1">
-        <v>0.00033514555559514933</v>
+        <v>0.00033546175108599093</v>
       </c>
       <c r="L22" s="1">
-        <v>0.00027000144375598592</v>
+        <v>0.00027085417726376167</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0020222132028897373</v>
+        <v>0.0020218895980936538</v>
       </c>
       <c r="N22" s="1">
-        <v>0.0019142766797069423</v>
+        <v>0.0019140590665750693</v>
       </c>
       <c r="O22" s="1">
-        <v>0.00032478638256148485</v>
+        <v>0.0003255555256660961</v>
       </c>
       <c r="P22" s="1">
-        <v>-7.9515155160856548e-05</v>
+        <v>-7.9667070001633296e-05</v>
       </c>
       <c r="Q22" s="1">
-        <v>0.00014837995345113415</v>
+        <v>0.00014989976797887558</v>
       </c>
       <c r="R22" s="1">
-        <v>9.0440026809771859e-05</v>
+        <v>8.8905473932556845e-05</v>
       </c>
       <c r="S22" s="1">
-        <v>-7.29068319772915e-06</v>
+        <v>-9.2838851698312172e-06</v>
       </c>
       <c r="T22" s="1">
-        <v>0.0001290856868992594</v>
+        <v>0.00012755148381044727</v>
       </c>
       <c r="U22" s="1">
-        <v>0.0001110162832364133</v>
+        <v>0.00010946766114039311</v>
       </c>
       <c r="V22" s="1">
-        <v>0.0010202887775112373</v>
+        <v>0.0010210796668203813</v>
       </c>
       <c r="W22" s="1">
-        <v>0.0036909996833885458</v>
+        <v>0.0036918542317275985</v>
       </c>
       <c r="X22" s="1">
-        <v>0.0031018109242410834</v>
+        <v>0.0031027982307668435</v>
       </c>
       <c r="Y22" s="1">
-        <v>0.0030521835615118799</v>
+        <v>0.0030533344647074587</v>
       </c>
       <c r="Z22" s="1">
-        <v>-0.00024211251387893686</v>
+        <v>-0.00024221011657039638</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.6869014206422196e-06</v>
+        <v>1.0083036832223474e-05</v>
       </c>
       <c r="AB22" s="1">
-        <v>-0.0002797980567982312</v>
+        <v>-0.00027892409427838333</v>
       </c>
       <c r="AC22" s="1">
-        <v>-0.00040033262607921342</v>
+        <v>-0.00039865402162681419</v>
       </c>
       <c r="AD22" s="1">
-        <v>-0.00021142302343477427</v>
+        <v>-0.00021016241342462725</v>
       </c>
       <c r="AE22" s="1">
-        <v>-2.1300930508672531e-05</v>
+        <v>-2.0460172197282723e-05</v>
       </c>
       <c r="AF22" s="1">
-        <v>-1.0969819930104656e-05</v>
+        <v>-1.1044181768673068e-05</v>
       </c>
       <c r="AG22" s="1">
-        <v>1.7003452339226649e-05</v>
+        <v>1.6642737841024262e-05</v>
       </c>
       <c r="AH22" s="1">
-        <v>-9.6010163130782534e-05</v>
+        <v>-9.5579285044669116e-05</v>
       </c>
       <c r="AI22" s="1">
-        <v>-0.0023063401908713496</v>
+        <v>-0.0023041549506998531</v>
       </c>
     </row>
     <row r="23">
@@ -2807,106 +2807,106 @@
         <v>48</v>
       </c>
       <c r="B23" s="1">
-        <v>0.05510310634025329</v>
+        <v>0.055280314669465987</v>
       </c>
       <c r="C23" s="1">
-        <v>-9.5717077923459059e-06</v>
+        <v>-9.1485995945669437e-06</v>
       </c>
       <c r="D23" s="1">
-        <v>-1.4746219871119735e-05</v>
+        <v>-1.4819559859276277e-05</v>
       </c>
       <c r="E23" s="1">
-        <v>1.9038412980075187e-07</v>
+        <v>1.9111069301303631e-07</v>
       </c>
       <c r="F23" s="1">
-        <v>0.00014358080305102033</v>
+        <v>0.00014352091070718423</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0005836356999005674</v>
+        <v>0.00058453139797889073</v>
       </c>
       <c r="H23" s="1">
-        <v>8.0538657238699574e-05</v>
+        <v>8.0889674896212867e-05</v>
       </c>
       <c r="I23" s="1">
-        <v>0.00057013382160985091</v>
+        <v>0.00057038861723722847</v>
       </c>
       <c r="J23" s="1">
-        <v>0.00077238395248175077</v>
+        <v>0.00077212829655680111</v>
       </c>
       <c r="K23" s="1">
-        <v>0.00054880521816930128</v>
+        <v>0.00054912120370216057</v>
       </c>
       <c r="L23" s="1">
-        <v>0.00083381817199853451</v>
+        <v>0.00083471801687879537</v>
       </c>
       <c r="M23" s="1">
-        <v>0.0030236058310321272</v>
+        <v>0.003023360280326578</v>
       </c>
       <c r="N23" s="1">
-        <v>0.0026582327290862835</v>
+        <v>0.0026580964336028203</v>
       </c>
       <c r="O23" s="1">
-        <v>0.00024458338733387655</v>
+        <v>0.00024534701779513709</v>
       </c>
       <c r="P23" s="1">
-        <v>0.00014868951782996543</v>
+        <v>0.00014852790007717758</v>
       </c>
       <c r="Q23" s="1">
-        <v>0.00017785419268018596</v>
+        <v>0.00017933967668695683</v>
       </c>
       <c r="R23" s="1">
-        <v>9.3871743006484283e-05</v>
+        <v>9.2483619022864843e-05</v>
       </c>
       <c r="S23" s="1">
-        <v>-5.6079343857187844e-07</v>
+        <v>-2.4284619037270297e-06</v>
       </c>
       <c r="T23" s="1">
-        <v>9.4746285503453633e-05</v>
+        <v>9.331877445525053e-05</v>
       </c>
       <c r="U23" s="1">
-        <v>7.2604863845638994e-05</v>
+        <v>7.118847575657202e-05</v>
       </c>
       <c r="V23" s="1">
-        <v>0.0010237795169709008</v>
+        <v>0.0010247818547826574</v>
       </c>
       <c r="W23" s="1">
-        <v>0.0031018109242410834</v>
+        <v>0.0031027982307668435</v>
       </c>
       <c r="X23" s="1">
-        <v>0.0046214212066241853</v>
+        <v>0.0046226282973295509</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.0038269830953325768</v>
+        <v>0.0038283245636070717</v>
       </c>
       <c r="Z23" s="1">
-        <v>-0.0002067722785244135</v>
+        <v>-0.00020687440748708613</v>
       </c>
       <c r="AA23" s="1">
-        <v>7.7692716934878842e-05</v>
+        <v>7.8095956337555185e-05</v>
       </c>
       <c r="AB23" s="1">
-        <v>-0.00046789774722273063</v>
+        <v>-0.00046699549069650578</v>
       </c>
       <c r="AC23" s="1">
-        <v>-0.00037899440289512211</v>
+        <v>-0.00037734500350142751</v>
       </c>
       <c r="AD23" s="1">
-        <v>-0.00019519531690427168</v>
+        <v>-0.0001938919718738198</v>
       </c>
       <c r="AE23" s="1">
-        <v>-8.3654210459185949e-05</v>
+        <v>-8.2816249389566386e-05</v>
       </c>
       <c r="AF23" s="1">
-        <v>-2.0439769367507852e-05</v>
+        <v>-2.0510283545094283e-05</v>
       </c>
       <c r="AG23" s="1">
-        <v>-0.0004137429209814308</v>
+        <v>-0.00041412271901550019</v>
       </c>
       <c r="AH23" s="1">
-        <v>-2.4966154561283874e-05</v>
+        <v>-2.4583298894115951e-05</v>
       </c>
       <c r="AI23" s="1">
-        <v>-0.0036031634998935939</v>
+        <v>-0.0036013155387573442</v>
       </c>
     </row>
     <row r="24">
@@ -2914,106 +2914,106 @@
         <v>49</v>
       </c>
       <c r="B24" s="1">
-        <v>0.10280679680573514</v>
+        <v>0.10298821575576686</v>
       </c>
       <c r="C24" s="1">
-        <v>-5.1490530926505081e-05</v>
+        <v>-5.1061133848233744e-05</v>
       </c>
       <c r="D24" s="1">
-        <v>-3.334311200503667e-05</v>
+        <v>-3.341954907391993e-05</v>
       </c>
       <c r="E24" s="1">
-        <v>3.3691857230022928e-07</v>
+        <v>3.3768330183125659e-07</v>
       </c>
       <c r="F24" s="1">
-        <v>0.00069832211350723261</v>
+        <v>0.00069835057831639773</v>
       </c>
       <c r="G24" s="1">
-        <v>0.0014808570481202338</v>
+        <v>0.0014818280495099978</v>
       </c>
       <c r="H24" s="1">
-        <v>0.0012406439888905277</v>
+        <v>0.0012411451432060745</v>
       </c>
       <c r="I24" s="1">
-        <v>0.0012816677600039558</v>
+        <v>0.0012820537542992116</v>
       </c>
       <c r="J24" s="1">
-        <v>0.0017848622337234277</v>
+        <v>0.0017846865085273432</v>
       </c>
       <c r="K24" s="1">
-        <v>0.0013740685193620039</v>
+        <v>0.001374503436026399</v>
       </c>
       <c r="L24" s="1">
-        <v>0.0019770426864075402</v>
+        <v>0.001978097150966863</v>
       </c>
       <c r="M24" s="1">
-        <v>0.0027733159243299192</v>
+        <v>0.0027730627979547472</v>
       </c>
       <c r="N24" s="1">
-        <v>0.002591507318392066</v>
+        <v>0.0025913672061562091</v>
       </c>
       <c r="O24" s="1">
-        <v>0.00028025822215264028</v>
+        <v>0.00028108956476705343</v>
       </c>
       <c r="P24" s="1">
-        <v>0.00019579031755848726</v>
+        <v>0.0001956804226815169</v>
       </c>
       <c r="Q24" s="1">
-        <v>0.00027754921601432945</v>
+        <v>0.0002790754528439127</v>
       </c>
       <c r="R24" s="1">
-        <v>0.00011091060839970874</v>
+        <v>0.00010938392672230242</v>
       </c>
       <c r="S24" s="1">
-        <v>1.6110739907131827e-06</v>
+        <v>-3.8578012009037044e-07</v>
       </c>
       <c r="T24" s="1">
-        <v>5.9141016341421673e-06</v>
+        <v>4.3895071609525993e-06</v>
       </c>
       <c r="U24" s="1">
-        <v>0.00044867180215855083</v>
+        <v>0.00044714402608699196</v>
       </c>
       <c r="V24" s="1">
-        <v>0.001044928469257808</v>
+        <v>0.001046175092324503</v>
       </c>
       <c r="W24" s="1">
-        <v>0.0030521835615118799</v>
+        <v>0.0030533344647074587</v>
       </c>
       <c r="X24" s="1">
-        <v>0.0038269830953325768</v>
+        <v>0.0038283245636070717</v>
       </c>
       <c r="Y24" s="1">
-        <v>0.0060181192451176143</v>
+        <v>0.0060197023473520933</v>
       </c>
       <c r="Z24" s="1">
-        <v>-0.00025201341356750331</v>
+        <v>-0.00025212346861566899</v>
       </c>
       <c r="AA24" s="1">
-        <v>0.00028632462633274139</v>
+        <v>0.00028673554223182502</v>
       </c>
       <c r="AB24" s="1">
-        <v>6.3240482893178133e-05</v>
+        <v>6.4112274406515155e-05</v>
       </c>
       <c r="AC24" s="1">
-        <v>-0.00038905432215107427</v>
+        <v>-0.00038731291716808964</v>
       </c>
       <c r="AD24" s="1">
-        <v>-8.2791533171887053e-05</v>
+        <v>-8.1433533488284085e-05</v>
       </c>
       <c r="AE24" s="1">
-        <v>-3.4108922658314476e-06</v>
+        <v>-2.5682863138457804e-06</v>
       </c>
       <c r="AF24" s="1">
-        <v>-5.2958136939784575e-06</v>
+        <v>-5.3679368083291439e-06</v>
       </c>
       <c r="AG24" s="1">
-        <v>2.7013920656180843e-05</v>
+        <v>2.6608758676932923e-05</v>
       </c>
       <c r="AH24" s="1">
-        <v>-3.8444874653800233e-05</v>
+        <v>-3.8001138661608634e-05</v>
       </c>
       <c r="AI24" s="1">
-        <v>-0.0044680593374207571</v>
+        <v>-0.0044663483416094527</v>
       </c>
     </row>
     <row r="25">
@@ -3021,106 +3021,106 @@
         <v>50</v>
       </c>
       <c r="B25" s="1">
-        <v>0.00049394647568021071</v>
+        <v>0.00048570016800170471</v>
       </c>
       <c r="C25" s="1">
-        <v>1.7043880377796739e-05</v>
+        <v>1.703249624486109e-05</v>
       </c>
       <c r="D25" s="1">
-        <v>2.4380910270669666e-06</v>
+        <v>2.440504676227692e-06</v>
       </c>
       <c r="E25" s="1">
-        <v>-1.8855388583301745e-08</v>
+        <v>-1.8880896116437346e-08</v>
       </c>
       <c r="F25" s="1">
-        <v>-0.00011809867867808874</v>
+        <v>-0.00011812177465150039</v>
       </c>
       <c r="G25" s="1">
-        <v>-5.3621536081370708e-05</v>
+        <v>-5.3661474261808658e-05</v>
       </c>
       <c r="H25" s="1">
-        <v>-7.6257997809397375e-05</v>
+        <v>-7.6287437757082831e-05</v>
       </c>
       <c r="I25" s="1">
-        <v>-0.00018331739696391623</v>
+        <v>-0.00018333719713183163</v>
       </c>
       <c r="J25" s="1">
-        <v>-9.3727905244657005e-05</v>
+        <v>-9.3723654982280771e-05</v>
       </c>
       <c r="K25" s="1">
-        <v>-8.8301389782695914e-05</v>
+        <v>-8.8325034545054363e-05</v>
       </c>
       <c r="L25" s="1">
-        <v>-0.00029959734920110214</v>
+        <v>-0.00029964542548491018</v>
       </c>
       <c r="M25" s="1">
-        <v>-0.00022006258845881193</v>
+        <v>-0.00022006907889646275</v>
       </c>
       <c r="N25" s="1">
-        <v>-0.00013326417041872827</v>
+        <v>-0.00013326755040911199</v>
       </c>
       <c r="O25" s="1">
-        <v>9.9586370740198407e-05</v>
+        <v>9.9567745906614351e-05</v>
       </c>
       <c r="P25" s="1">
-        <v>3.2771132055161784e-05</v>
+        <v>3.2782889101071736e-05</v>
       </c>
       <c r="Q25" s="1">
-        <v>3.0771138346440715e-05</v>
+        <v>3.0721731431154108e-05</v>
       </c>
       <c r="R25" s="1">
-        <v>-4.706742944154339e-05</v>
+        <v>-4.7014779429000136e-05</v>
       </c>
       <c r="S25" s="1">
-        <v>-3.4565882891118252e-05</v>
+        <v>-3.4490693020475184e-05</v>
       </c>
       <c r="T25" s="1">
-        <v>-1.415044953726423e-05</v>
+        <v>-1.4100512438041345e-05</v>
       </c>
       <c r="U25" s="1">
-        <v>-4.3680206441036834e-05</v>
+        <v>-4.363070286970798e-05</v>
       </c>
       <c r="V25" s="1">
-        <v>-4.3537476979998616e-05</v>
+        <v>-4.365518929645886e-05</v>
       </c>
       <c r="W25" s="1">
-        <v>-0.00024211251387893686</v>
+        <v>-0.00024221011657039638</v>
       </c>
       <c r="X25" s="1">
-        <v>-0.0002067722785244135</v>
+        <v>-0.00020687440748708613</v>
       </c>
       <c r="Y25" s="1">
-        <v>-0.00025201341356750331</v>
+        <v>-0.00025212346861566899</v>
       </c>
       <c r="Z25" s="1">
-        <v>0.00013109594446500796</v>
+        <v>0.00013110775455529768</v>
       </c>
       <c r="AA25" s="1">
-        <v>-1.1473670897181444e-05</v>
+        <v>-1.1496810079778212e-05</v>
       </c>
       <c r="AB25" s="1">
-        <v>-7.344504960223642e-06</v>
+        <v>-7.3746443255731282e-06</v>
       </c>
       <c r="AC25" s="1">
-        <v>2.9167467439685284e-05</v>
+        <v>2.9097364910560071e-05</v>
       </c>
       <c r="AD25" s="1">
-        <v>8.3251017500502569e-06</v>
+        <v>8.2650454317234041e-06</v>
       </c>
       <c r="AE25" s="1">
-        <v>1.0900795457295389e-05</v>
+        <v>1.0864807929789812e-05</v>
       </c>
       <c r="AF25" s="1">
-        <v>8.1948204305922917e-06</v>
+        <v>8.1995916351229465e-06</v>
       </c>
       <c r="AG25" s="1">
-        <v>-7.878238979716642e-05</v>
+        <v>-7.8775233435716534e-05</v>
       </c>
       <c r="AH25" s="1">
-        <v>-3.643446001217829e-06</v>
+        <v>-3.6744155247174436e-06</v>
       </c>
       <c r="AI25" s="1">
-        <v>1.1928478629545501e-05</v>
+        <v>1.1901767045954863e-05</v>
       </c>
     </row>
     <row r="26">
@@ -3128,106 +3128,106 @@
         <v>51</v>
       </c>
       <c r="B26" s="1">
-        <v>4.5183987236620196</v>
+        <v>4.5184054821027049</v>
       </c>
       <c r="C26" s="1">
-        <v>1.2655537415415209e-06</v>
+        <v>1.2971106044525288e-06</v>
       </c>
       <c r="D26" s="1">
-        <v>-2.3135685107409824e-06</v>
+        <v>-2.318174994157254e-06</v>
       </c>
       <c r="E26" s="1">
-        <v>-1.577508248251216e-08</v>
+        <v>-1.5730525886711247e-08</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.00032910284523235661</v>
+        <v>-0.00032914750589769473</v>
       </c>
       <c r="G26" s="1">
-        <v>-0.00014017992309831357</v>
+        <v>-0.00014013264826896079</v>
       </c>
       <c r="H26" s="1">
-        <v>5.4140611069456422e-05</v>
+        <v>5.4185832681908177e-05</v>
       </c>
       <c r="I26" s="1">
-        <v>0.00029842096755970313</v>
+        <v>0.00029842893781968118</v>
       </c>
       <c r="J26" s="1">
-        <v>-3.2864155674861581e-05</v>
+        <v>-3.293249802066605e-05</v>
       </c>
       <c r="K26" s="1">
-        <v>-0.00018935942338966431</v>
+        <v>-0.00018935105215490635</v>
       </c>
       <c r="L26" s="1">
-        <v>-9.3359109020845681e-05</v>
+        <v>-9.3307477727147385e-05</v>
       </c>
       <c r="M26" s="1">
-        <v>3.2586273834562802e-05</v>
+        <v>3.2547988835394817e-05</v>
       </c>
       <c r="N26" s="1">
-        <v>2.8569475604282022e-05</v>
+        <v>2.8552233570940089e-05</v>
       </c>
       <c r="O26" s="1">
-        <v>-0.00025446021819621617</v>
+        <v>-0.00025441639759160372</v>
       </c>
       <c r="P26" s="1">
-        <v>-0.00015133954198028499</v>
+        <v>-0.00015138500222011664</v>
       </c>
       <c r="Q26" s="1">
-        <v>-0.00015626837671342436</v>
+        <v>-0.00015617379926339181</v>
       </c>
       <c r="R26" s="1">
-        <v>7.6719584510547109e-05</v>
+        <v>7.6648640624824797e-05</v>
       </c>
       <c r="S26" s="1">
-        <v>7.06083323108789e-05</v>
+        <v>7.0468009777775666e-05</v>
       </c>
       <c r="T26" s="1">
-        <v>1.874010255916163e-05</v>
+        <v>1.8680091532220799e-05</v>
       </c>
       <c r="U26" s="1">
-        <v>0.00016252701259978611</v>
+        <v>0.0001624547930171704</v>
       </c>
       <c r="V26" s="1">
-        <v>7.4921596938549125e-05</v>
+        <v>7.5628287774842599e-05</v>
       </c>
       <c r="W26" s="1">
-        <v>9.6869014206422196e-06</v>
+        <v>1.0083036832223474e-05</v>
       </c>
       <c r="X26" s="1">
-        <v>7.7692716934878842e-05</v>
+        <v>7.8095956337555185e-05</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.00028632462633274139</v>
+        <v>0.00028673554223182502</v>
       </c>
       <c r="Z26" s="1">
-        <v>-1.1473670897181444e-05</v>
+        <v>-1.1496810079778212e-05</v>
       </c>
       <c r="AA26" s="1">
-        <v>0.00099144247678501374</v>
+        <v>0.00099154428750107201</v>
       </c>
       <c r="AB26" s="1">
-        <v>9.2324923839546508e-05</v>
+        <v>9.2442233864804902e-05</v>
       </c>
       <c r="AC26" s="1">
-        <v>-1.517974319102959e-05</v>
+        <v>-1.4973262876394013e-05</v>
       </c>
       <c r="AD26" s="1">
-        <v>3.5642171720563755e-05</v>
+        <v>3.5791349820744404e-05</v>
       </c>
       <c r="AE26" s="1">
-        <v>1.5069722222695244e-05</v>
+        <v>1.5190971794482174e-05</v>
       </c>
       <c r="AF26" s="1">
-        <v>-1.4146541186949306e-05</v>
+        <v>-1.4164162094148888e-05</v>
       </c>
       <c r="AG26" s="1">
-        <v>-4.3410768808381127e-06</v>
+        <v>-4.3437273826298453e-06</v>
       </c>
       <c r="AH26" s="1">
-        <v>-8.3823401668065738e-05</v>
+        <v>-8.3745360883607766e-05</v>
       </c>
       <c r="AI26" s="1">
-        <v>-1.5269908431510834e-05</v>
+        <v>-1.5302206656640392e-05</v>
       </c>
     </row>
     <row r="27">
@@ -3235,106 +3235,106 @@
         <v>52</v>
       </c>
       <c r="B27" s="1">
-        <v>-0.029719838015395305</v>
+        <v>-0.029619194959717904</v>
       </c>
       <c r="C27" s="1">
-        <v>0.00013356223390172865</v>
+        <v>0.00013348757485753875</v>
       </c>
       <c r="D27" s="1">
-        <v>-1.624120138801413e-05</v>
+        <v>-1.6219783736747039e-05</v>
       </c>
       <c r="E27" s="1">
-        <v>2.1722774254655125e-07</v>
+        <v>2.1697693665274262e-07</v>
       </c>
       <c r="F27" s="1">
-        <v>0.0001324009512291913</v>
+        <v>0.00013258464283199146</v>
       </c>
       <c r="G27" s="1">
-        <v>3.8504958845782906e-05</v>
+        <v>3.8600171725805413e-05</v>
       </c>
       <c r="H27" s="1">
-        <v>0.0008313003445649704</v>
+        <v>0.00083129357871324604</v>
       </c>
       <c r="I27" s="1">
-        <v>0.0008007981067031573</v>
+        <v>0.00080104943008802148</v>
       </c>
       <c r="J27" s="1">
-        <v>0.00032457542267697558</v>
+        <v>0.00032461544543753006</v>
       </c>
       <c r="K27" s="1">
-        <v>0.00029090483733027177</v>
+        <v>0.00029099613388316233</v>
       </c>
       <c r="L27" s="1">
-        <v>0.00023328268872757065</v>
+        <v>0.00023329937459805631</v>
       </c>
       <c r="M27" s="1">
-        <v>7.4833452486069724e-05</v>
+        <v>7.5226980097970516e-05</v>
       </c>
       <c r="N27" s="1">
-        <v>-5.2887370634620377e-05</v>
+        <v>-5.2827399760034185e-05</v>
       </c>
       <c r="O27" s="1">
-        <v>-0.00046734704395442166</v>
+        <v>-0.00046753039124638698</v>
       </c>
       <c r="P27" s="1">
-        <v>-9.5606798937157892e-05</v>
+        <v>-9.5600249300901909e-05</v>
       </c>
       <c r="Q27" s="1">
-        <v>-0.00051156819443302112</v>
+        <v>-0.00051157164252362605</v>
       </c>
       <c r="R27" s="1">
-        <v>-0.00021215051267309878</v>
+        <v>-0.00021243013952527371</v>
       </c>
       <c r="S27" s="1">
-        <v>-2.6508417137219905e-05</v>
+        <v>-2.655963142805199e-05</v>
       </c>
       <c r="T27" s="1">
-        <v>-0.00020892601191444156</v>
+        <v>-0.00020916221684381866</v>
       </c>
       <c r="U27" s="1">
-        <v>5.8449844738702947e-05</v>
+        <v>5.8043301962052395e-05</v>
       </c>
       <c r="V27" s="1">
-        <v>-0.00025310321532276994</v>
+        <v>-0.00025161792545769376</v>
       </c>
       <c r="W27" s="1">
-        <v>-0.0002797980567982312</v>
+        <v>-0.00027892409427838333</v>
       </c>
       <c r="X27" s="1">
-        <v>-0.00046789774722273063</v>
+        <v>-0.00046699549069650578</v>
       </c>
       <c r="Y27" s="1">
-        <v>6.3240482893178133e-05</v>
+        <v>6.4112274406515155e-05</v>
       </c>
       <c r="Z27" s="1">
-        <v>-7.344504960223642e-06</v>
+        <v>-7.3746443255731282e-06</v>
       </c>
       <c r="AA27" s="1">
-        <v>9.2324923839546508e-05</v>
+        <v>9.2442233864804902e-05</v>
       </c>
       <c r="AB27" s="1">
-        <v>0.0026079186679059856</v>
+        <v>0.0026069558267500154</v>
       </c>
       <c r="AC27" s="1">
-        <v>0.00078093067278797105</v>
+        <v>0.00078045211958530558</v>
       </c>
       <c r="AD27" s="1">
-        <v>0.00081781861922218676</v>
+        <v>0.00081748962915713385</v>
       </c>
       <c r="AE27" s="1">
-        <v>0.00075726586087959962</v>
+        <v>0.00075708146275862477</v>
       </c>
       <c r="AF27" s="1">
-        <v>-1.6537558506664969e-05</v>
+        <v>-1.6512081284590672e-05</v>
       </c>
       <c r="AG27" s="1">
-        <v>0.0014040279257729056</v>
+        <v>0.0014027993340197621</v>
       </c>
       <c r="AH27" s="1">
-        <v>-3.9542928370614374e-05</v>
+        <v>-3.9572065897156092e-05</v>
       </c>
       <c r="AI27" s="1">
-        <v>-0.0003641020609104575</v>
+        <v>-0.00036521460366246592</v>
       </c>
     </row>
     <row r="28">
@@ -3342,106 +3342,106 @@
         <v>53</v>
       </c>
       <c r="B28" s="1">
-        <v>-0.1207606509205465</v>
+        <v>-0.12060901760129455</v>
       </c>
       <c r="C28" s="1">
-        <v>3.6018549702649739e-05</v>
+        <v>3.5906606022980759e-05</v>
       </c>
       <c r="D28" s="1">
-        <v>9.9722643640448886e-07</v>
+        <v>1.0020687029202533e-06</v>
       </c>
       <c r="E28" s="1">
-        <v>-5.2305234655144031e-08</v>
+        <v>-5.233432742782789e-08</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.00013050618218950379</v>
+        <v>-0.00013031174901085435</v>
       </c>
       <c r="G28" s="1">
-        <v>0.00019367917905725143</v>
+        <v>0.00019358904626544686</v>
       </c>
       <c r="H28" s="1">
-        <v>0.00012474809821146592</v>
+        <v>0.00012496038602730769</v>
       </c>
       <c r="I28" s="1">
-        <v>3.8953113062006797e-05</v>
+        <v>3.9326919599426673e-05</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.00014329153982553435</v>
+        <v>-0.00014311111833606276</v>
       </c>
       <c r="K28" s="1">
-        <v>9.6569270227219416e-05</v>
+        <v>9.6735004546593707e-05</v>
       </c>
       <c r="L28" s="1">
-        <v>9.996348617431804e-05</v>
+        <v>0.00010007515246141961</v>
       </c>
       <c r="M28" s="1">
-        <v>-0.00038415162587905009</v>
+        <v>-0.00038361733544201547</v>
       </c>
       <c r="N28" s="1">
-        <v>-0.00018193685850591322</v>
+        <v>-0.00018187408605579471</v>
       </c>
       <c r="O28" s="1">
-        <v>0.0010045878634789454</v>
+        <v>0.0010042069158438011</v>
       </c>
       <c r="P28" s="1">
-        <v>4.4696501391709286e-05</v>
+        <v>4.4662224686543568e-05</v>
       </c>
       <c r="Q28" s="1">
-        <v>-3.1283870040078616e-06</v>
+        <v>-3.2260322206749664e-06</v>
       </c>
       <c r="R28" s="1">
-        <v>-1.8808264159679306e-05</v>
+        <v>-1.892949475234499e-05</v>
       </c>
       <c r="S28" s="1">
-        <v>-9.3521426413956717e-05</v>
+        <v>-9.3435530137901679e-05</v>
       </c>
       <c r="T28" s="1">
-        <v>1.3071063921402809e-05</v>
+        <v>1.2953436054778666e-05</v>
       </c>
       <c r="U28" s="1">
-        <v>-8.7928939257170442e-05</v>
+        <v>-8.7989812938883e-05</v>
       </c>
       <c r="V28" s="1">
-        <v>-0.0002182420867960467</v>
+        <v>-0.00021547988097651881</v>
       </c>
       <c r="W28" s="1">
-        <v>-0.00040033262607921342</v>
+        <v>-0.00039865402162681419</v>
       </c>
       <c r="X28" s="1">
-        <v>-0.00037899440289512211</v>
+        <v>-0.00037734500350142751</v>
       </c>
       <c r="Y28" s="1">
-        <v>-0.00038905432215107427</v>
+        <v>-0.00038731291716808964</v>
       </c>
       <c r="Z28" s="1">
-        <v>2.9167467439685284e-05</v>
+        <v>2.9097364910560071e-05</v>
       </c>
       <c r="AA28" s="1">
-        <v>-1.517974319102959e-05</v>
+        <v>-1.4973262876394013e-05</v>
       </c>
       <c r="AB28" s="1">
-        <v>0.00078093067278797105</v>
+        <v>0.00078045211958530558</v>
       </c>
       <c r="AC28" s="1">
-        <v>0.0030011128894324697</v>
+        <v>0.0030001524582718561</v>
       </c>
       <c r="AD28" s="1">
-        <v>0.00077609571084421734</v>
+        <v>0.00077574445734187745</v>
       </c>
       <c r="AE28" s="1">
-        <v>0.00078713993171308089</v>
+        <v>0.00078697545679939939</v>
       </c>
       <c r="AF28" s="1">
-        <v>-1.3132983855679586e-05</v>
+        <v>-1.3115504299860544e-05</v>
       </c>
       <c r="AG28" s="1">
-        <v>2.8006921631922813e-05</v>
+        <v>2.777099795667334e-05</v>
       </c>
       <c r="AH28" s="1">
-        <v>-2.8994776501056068e-05</v>
+        <v>-2.9016860731711906e-05</v>
       </c>
       <c r="AI28" s="1">
-        <v>-0.0002315135107170789</v>
+        <v>-0.00023327533986443371</v>
       </c>
     </row>
     <row r="29">
@@ -3449,106 +3449,106 @@
         <v>54</v>
       </c>
       <c r="B29" s="1">
-        <v>-0.096892115056395819</v>
+        <v>-0.096759686466759351</v>
       </c>
       <c r="C29" s="1">
-        <v>8.4478008515147991e-05</v>
+        <v>8.4432833747047036e-05</v>
       </c>
       <c r="D29" s="1">
-        <v>1.7766853539537218e-06</v>
+        <v>1.7928452363512139e-06</v>
       </c>
       <c r="E29" s="1">
-        <v>-1.7726683394529271e-08</v>
+        <v>-1.7861251314963683e-08</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.00020840439676645238</v>
+        <v>-0.00020830371312508393</v>
       </c>
       <c r="G29" s="1">
-        <v>-5.157229170116767e-06</v>
+        <v>-4.8643516756680105e-06</v>
       </c>
       <c r="H29" s="1">
-        <v>7.8688988978744021e-05</v>
+        <v>7.8889996787906999e-05</v>
       </c>
       <c r="I29" s="1">
-        <v>-5.3559941448758598e-05</v>
+        <v>-5.3285898904157776e-05</v>
       </c>
       <c r="J29" s="1">
-        <v>-5.533329262149284e-05</v>
+        <v>-5.5184564531761594e-05</v>
       </c>
       <c r="K29" s="1">
-        <v>0.00010418293855289455</v>
+        <v>0.0001042264218092853</v>
       </c>
       <c r="L29" s="1">
-        <v>6.3570387819939468e-05</v>
+        <v>6.3654548704147586e-05</v>
       </c>
       <c r="M29" s="1">
-        <v>-2.7466781197101146e-06</v>
+        <v>-2.2198173791241021e-06</v>
       </c>
       <c r="N29" s="1">
-        <v>-0.00016519126492804285</v>
+        <v>-0.00016504332285276739</v>
       </c>
       <c r="O29" s="1">
-        <v>-0.00015049816258301391</v>
+        <v>-0.00015093501953635053</v>
       </c>
       <c r="P29" s="1">
-        <v>4.2202548481914394e-05</v>
+        <v>4.2043649106421327e-05</v>
       </c>
       <c r="Q29" s="1">
-        <v>-0.00010253632380451705</v>
+        <v>-0.00010253843728468624</v>
       </c>
       <c r="R29" s="1">
-        <v>4.324738019545902e-06</v>
+        <v>4.4386814656974846e-06</v>
       </c>
       <c r="S29" s="1">
-        <v>-8.9532176432434427e-05</v>
+        <v>-8.9403800585542736e-05</v>
       </c>
       <c r="T29" s="1">
-        <v>-3.6489378424410456e-05</v>
+        <v>-3.6340200214661711e-05</v>
       </c>
       <c r="U29" s="1">
-        <v>-0.0001091055841504554</v>
+        <v>-0.00010889695296658299</v>
       </c>
       <c r="V29" s="1">
-        <v>-4.703608763296229e-05</v>
+        <v>-4.4679485724224246e-05</v>
       </c>
       <c r="W29" s="1">
-        <v>-0.00021142302343477427</v>
+        <v>-0.00021016241342462725</v>
       </c>
       <c r="X29" s="1">
-        <v>-0.00019519531690427168</v>
+        <v>-0.0001938919718738198</v>
       </c>
       <c r="Y29" s="1">
-        <v>-8.2791533171887053e-05</v>
+        <v>-8.1433533488284085e-05</v>
       </c>
       <c r="Z29" s="1">
-        <v>8.3251017500502569e-06</v>
+        <v>8.2650454317234041e-06</v>
       </c>
       <c r="AA29" s="1">
-        <v>3.5642171720563755e-05</v>
+        <v>3.5791349820744404e-05</v>
       </c>
       <c r="AB29" s="1">
-        <v>0.00081781861922218676</v>
+        <v>0.00081748962915713385</v>
       </c>
       <c r="AC29" s="1">
-        <v>0.00077609571084421734</v>
+        <v>0.00077574445734187745</v>
       </c>
       <c r="AD29" s="1">
-        <v>0.0017041989574858188</v>
+        <v>0.0017043518322858455</v>
       </c>
       <c r="AE29" s="1">
-        <v>0.00078038148153157234</v>
+        <v>0.00078032338053041586</v>
       </c>
       <c r="AF29" s="1">
-        <v>-1.3135980067911757e-05</v>
+        <v>-1.3134850370276575e-05</v>
       </c>
       <c r="AG29" s="1">
-        <v>-9.5617466619221658e-05</v>
+        <v>-9.588779748412172e-05</v>
       </c>
       <c r="AH29" s="1">
-        <v>0.00016787332760798308</v>
+        <v>0.00016799270878013845</v>
       </c>
       <c r="AI29" s="1">
-        <v>-0.00049493725504928072</v>
+        <v>-0.00049672316567001061</v>
       </c>
     </row>
     <row r="30">
@@ -3556,106 +3556,106 @@
         <v>55</v>
       </c>
       <c r="B30" s="1">
-        <v>-0.021026188054069844</v>
+        <v>-0.020949380229826408</v>
       </c>
       <c r="C30" s="1">
-        <v>7.6695965527998262e-05</v>
+        <v>7.6617553245312344e-05</v>
       </c>
       <c r="D30" s="1">
-        <v>8.487245207729015e-07</v>
+        <v>8.6128256701267975e-07</v>
       </c>
       <c r="E30" s="1">
-        <v>-3.3882558595311323e-08</v>
+        <v>-3.3990372793663547e-08</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.00030774076146367893</v>
+        <v>-0.00030765779270407038</v>
       </c>
       <c r="G30" s="1">
-        <v>-3.1585154077989289e-05</v>
+        <v>-3.1518877984254437e-05</v>
       </c>
       <c r="H30" s="1">
-        <v>-0.00029993085834891637</v>
+        <v>-0.00029987477499125682</v>
       </c>
       <c r="I30" s="1">
-        <v>-0.00013394412750209568</v>
+        <v>-0.00013376227481682636</v>
       </c>
       <c r="J30" s="1">
-        <v>-0.0001909090230916104</v>
+        <v>-0.00019088401157985209</v>
       </c>
       <c r="K30" s="1">
-        <v>-2.1851853514240653e-05</v>
+        <v>-2.1788348348834386e-05</v>
       </c>
       <c r="L30" s="1">
-        <v>-0.00021059699516398417</v>
+        <v>-0.00021060086451884781</v>
       </c>
       <c r="M30" s="1">
-        <v>8.4829266834013893e-05</v>
+        <v>8.5104492900944795e-05</v>
       </c>
       <c r="N30" s="1">
-        <v>-4.9810358773324918e-05</v>
+        <v>-4.9756753791821472e-05</v>
       </c>
       <c r="O30" s="1">
-        <v>-0.00023249580819562955</v>
+        <v>-0.00023270938346594213</v>
       </c>
       <c r="P30" s="1">
-        <v>9.1416859703396776e-05</v>
+        <v>9.1349858866628813e-05</v>
       </c>
       <c r="Q30" s="1">
-        <v>0.00010867499151273315</v>
+        <v>0.00010865995116393103</v>
       </c>
       <c r="R30" s="1">
-        <v>3.5392185713120205e-05</v>
+        <v>3.5193778356397117e-05</v>
       </c>
       <c r="S30" s="1">
-        <v>3.3010360078103169e-05</v>
+        <v>3.305640638191689e-05</v>
       </c>
       <c r="T30" s="1">
-        <v>0.00021761130409639427</v>
+        <v>0.00021765638484483492</v>
       </c>
       <c r="U30" s="1">
-        <v>0.00010065081723502215</v>
+        <v>0.00010066704517814945</v>
       </c>
       <c r="V30" s="1">
-        <v>3.0517426843605254e-05</v>
+        <v>3.2047790430182299e-05</v>
       </c>
       <c r="W30" s="1">
-        <v>-2.1300930508672531e-05</v>
+        <v>-2.0460172197282723e-05</v>
       </c>
       <c r="X30" s="1">
-        <v>-8.3654210459185949e-05</v>
+        <v>-8.2816249389566386e-05</v>
       </c>
       <c r="Y30" s="1">
-        <v>-3.4108922658314476e-06</v>
+        <v>-2.5682863138457804e-06</v>
       </c>
       <c r="Z30" s="1">
-        <v>1.0900795457295389e-05</v>
+        <v>1.0864807929789812e-05</v>
       </c>
       <c r="AA30" s="1">
-        <v>1.5069722222695244e-05</v>
+        <v>1.5190971794482174e-05</v>
       </c>
       <c r="AB30" s="1">
-        <v>0.00075726586087959962</v>
+        <v>0.00075708146275862477</v>
       </c>
       <c r="AC30" s="1">
-        <v>0.00078713993171308089</v>
+        <v>0.00078697545679939939</v>
       </c>
       <c r="AD30" s="1">
-        <v>0.00078038148153157234</v>
+        <v>0.00078032338053041586</v>
       </c>
       <c r="AE30" s="1">
-        <v>0.0013925535545286864</v>
+        <v>0.0013925486424309307</v>
       </c>
       <c r="AF30" s="1">
-        <v>-9.0915711444416216e-06</v>
+        <v>-9.1005615912336717e-06</v>
       </c>
       <c r="AG30" s="1">
-        <v>4.7451106291427486e-05</v>
+        <v>4.7054256993537494e-05</v>
       </c>
       <c r="AH30" s="1">
-        <v>-2.1885818613790007e-05</v>
+        <v>-2.178312243663542e-05</v>
       </c>
       <c r="AI30" s="1">
-        <v>-0.000723857348972636</v>
+        <v>-0.00072478232261304434</v>
       </c>
     </row>
     <row r="31">
@@ -3663,106 +3663,106 @@
         <v>56</v>
       </c>
       <c r="B31" s="1">
-        <v>-0.00022317035269949981</v>
+        <v>-0.00023822987192168366</v>
       </c>
       <c r="C31" s="1">
-        <v>4.1541907824473162e-06</v>
+        <v>4.1526504448567318e-06</v>
       </c>
       <c r="D31" s="1">
-        <v>8.9705994768908749e-07</v>
+        <v>8.9566468710405384e-07</v>
       </c>
       <c r="E31" s="1">
-        <v>-8.7979821706091228e-09</v>
+        <v>-8.7858198841563254e-09</v>
       </c>
       <c r="F31" s="1">
-        <v>-6.5319551372293406e-06</v>
+        <v>-6.5349142992832988e-06</v>
       </c>
       <c r="G31" s="1">
-        <v>-3.1270047416422043e-06</v>
+        <v>-3.1219584513314026e-06</v>
       </c>
       <c r="H31" s="1">
-        <v>-1.4384790905600252e-05</v>
+        <v>-1.4403622927687722e-05</v>
       </c>
       <c r="I31" s="1">
-        <v>4.1096559598746316e-05</v>
+        <v>4.1076569387497571e-05</v>
       </c>
       <c r="J31" s="1">
-        <v>-6.2109427909475077e-07</v>
+        <v>-6.2528403432598155e-07</v>
       </c>
       <c r="K31" s="1">
-        <v>-1.242640000420251e-05</v>
+        <v>-1.2440144133851511e-05</v>
       </c>
       <c r="L31" s="1">
-        <v>-2.9573377166804376e-05</v>
+        <v>-2.95887091056339e-05</v>
       </c>
       <c r="M31" s="1">
-        <v>-4.9473496396261083e-06</v>
+        <v>-5.0061487570539289e-06</v>
       </c>
       <c r="N31" s="1">
-        <v>-1.3557596760123148e-05</v>
+        <v>-1.3559413908074817e-05</v>
       </c>
       <c r="O31" s="1">
-        <v>6.2950663784039872e-06</v>
+        <v>6.3361311039926405e-06</v>
       </c>
       <c r="P31" s="1">
-        <v>-9.2170658087262832e-06</v>
+        <v>-9.198748865140623e-06</v>
       </c>
       <c r="Q31" s="1">
-        <v>1.4215581820925611e-05</v>
+        <v>1.420966022217161e-05</v>
       </c>
       <c r="R31" s="1">
-        <v>1.2714178479155433e-05</v>
+        <v>1.2696943429794656e-05</v>
       </c>
       <c r="S31" s="1">
-        <v>-5.4679806765953708e-06</v>
+        <v>-5.4652450479372532e-06</v>
       </c>
       <c r="T31" s="1">
-        <v>-1.2262030127587788e-05</v>
+        <v>-1.2271406114615303e-05</v>
       </c>
       <c r="U31" s="1">
-        <v>1.878946900336399e-05</v>
+        <v>1.8783416111344898e-05</v>
       </c>
       <c r="V31" s="1">
-        <v>-2.510252179523074e-06</v>
+        <v>-2.595681288296738e-06</v>
       </c>
       <c r="W31" s="1">
-        <v>-1.0969819930104656e-05</v>
+        <v>-1.1044181768673068e-05</v>
       </c>
       <c r="X31" s="1">
-        <v>-2.0439769367507852e-05</v>
+        <v>-2.0510283545094283e-05</v>
       </c>
       <c r="Y31" s="1">
-        <v>-5.2958136939784575e-06</v>
+        <v>-5.3679368083291439e-06</v>
       </c>
       <c r="Z31" s="1">
-        <v>8.1948204305922917e-06</v>
+        <v>8.1995916351229465e-06</v>
       </c>
       <c r="AA31" s="1">
-        <v>-1.4146541186949306e-05</v>
+        <v>-1.4164162094148888e-05</v>
       </c>
       <c r="AB31" s="1">
-        <v>-1.6537558506664969e-05</v>
+        <v>-1.6512081284590672e-05</v>
       </c>
       <c r="AC31" s="1">
-        <v>-1.3132983855679586e-05</v>
+        <v>-1.3115504299860544e-05</v>
       </c>
       <c r="AD31" s="1">
-        <v>-1.3135980067911757e-05</v>
+        <v>-1.3134850370276575e-05</v>
       </c>
       <c r="AE31" s="1">
-        <v>-9.0915711444416216e-06</v>
+        <v>-9.1005615912336717e-06</v>
       </c>
       <c r="AF31" s="1">
-        <v>1.859856923766249e-05</v>
+        <v>1.8599613997441251e-05</v>
       </c>
       <c r="AG31" s="1">
-        <v>-5.2267177061783468e-05</v>
+        <v>-5.2242992357662494e-05</v>
       </c>
       <c r="AH31" s="1">
-        <v>-7.2129469137212883e-05</v>
+        <v>-7.2131143512936592e-05</v>
       </c>
       <c r="AI31" s="1">
-        <v>-0.00029877450971993826</v>
+        <v>-0.00029868492141306592</v>
       </c>
     </row>
     <row r="32">
@@ -3770,106 +3770,106 @@
         <v>57</v>
       </c>
       <c r="B32" s="1">
-        <v>-0.30553314584034941</v>
+        <v>-0.30548248897761521</v>
       </c>
       <c r="C32" s="1">
-        <v>0.00020710799942020956</v>
+        <v>0.00020691904777094027</v>
       </c>
       <c r="D32" s="1">
-        <v>-3.9228291597210663e-05</v>
+        <v>-3.9222352389803533e-05</v>
       </c>
       <c r="E32" s="1">
-        <v>4.8566585989150069e-07</v>
+        <v>4.8555487422392973e-07</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.0003190860430732842</v>
+        <v>-0.00031898105588199291</v>
       </c>
       <c r="G32" s="1">
-        <v>-9.9578717831078772e-05</v>
+        <v>-9.9466753123144021e-05</v>
       </c>
       <c r="H32" s="1">
-        <v>0.0015306419737571133</v>
+        <v>0.0015307312507497018</v>
       </c>
       <c r="I32" s="1">
-        <v>-0.00017382711948333088</v>
+        <v>-0.00017362786738672059</v>
       </c>
       <c r="J32" s="1">
-        <v>0.00012727632572262244</v>
+        <v>0.00012736446351298801</v>
       </c>
       <c r="K32" s="1">
-        <v>0.00032090980639919511</v>
+        <v>0.0003209557824896507</v>
       </c>
       <c r="L32" s="1">
-        <v>0.00043169606570728561</v>
+        <v>0.00043162195916210053</v>
       </c>
       <c r="M32" s="1">
-        <v>-0.00038923973069070195</v>
+        <v>-0.00038904825937731424</v>
       </c>
       <c r="N32" s="1">
-        <v>3.3733079687679399e-05</v>
+        <v>3.3766524974406138e-05</v>
       </c>
       <c r="O32" s="1">
-        <v>-6.6477564774155076e-05</v>
+        <v>-6.6587311333537839e-05</v>
       </c>
       <c r="P32" s="1">
-        <v>-0.00033822251339411672</v>
+        <v>-0.00033817467731770984</v>
       </c>
       <c r="Q32" s="1">
-        <v>-0.00033315234725321812</v>
+        <v>-0.00033350677976503153</v>
       </c>
       <c r="R32" s="1">
-        <v>-8.8888418991317844e-05</v>
+        <v>-8.9811991759721627e-05</v>
       </c>
       <c r="S32" s="1">
-        <v>0.00052095509195258273</v>
+        <v>0.00052060695751364461</v>
       </c>
       <c r="T32" s="1">
-        <v>0.00029097501126850063</v>
+        <v>0.00029037738598188152</v>
       </c>
       <c r="U32" s="1">
-        <v>0.00081544827374738227</v>
+        <v>0.00081445922192247347</v>
       </c>
       <c r="V32" s="1">
-        <v>-0.00030434473930856859</v>
+        <v>-0.00030505296664115459</v>
       </c>
       <c r="W32" s="1">
-        <v>1.7003452339226649e-05</v>
+        <v>1.6642737841024262e-05</v>
       </c>
       <c r="X32" s="1">
-        <v>-0.0004137429209814308</v>
+        <v>-0.00041412271901550019</v>
       </c>
       <c r="Y32" s="1">
-        <v>2.7013920656180843e-05</v>
+        <v>2.6608758676932923e-05</v>
       </c>
       <c r="Z32" s="1">
-        <v>-7.878238979716642e-05</v>
+        <v>-7.8775233435716534e-05</v>
       </c>
       <c r="AA32" s="1">
-        <v>-4.3410768808381127e-06</v>
+        <v>-4.3437273826298453e-06</v>
       </c>
       <c r="AB32" s="1">
-        <v>0.0014040279257729056</v>
+        <v>0.0014027993340197621</v>
       </c>
       <c r="AC32" s="1">
-        <v>2.8006921631922813e-05</v>
+        <v>2.777099795667334e-05</v>
       </c>
       <c r="AD32" s="1">
-        <v>-9.5617466619221658e-05</v>
+        <v>-9.588779748412172e-05</v>
       </c>
       <c r="AE32" s="1">
-        <v>4.7451106291427486e-05</v>
+        <v>4.7054256993537494e-05</v>
       </c>
       <c r="AF32" s="1">
-        <v>-5.2267177061783468e-05</v>
+        <v>-5.2242992357662494e-05</v>
       </c>
       <c r="AG32" s="1">
-        <v>0.0063763856460249064</v>
+        <v>0.0063760203411970251</v>
       </c>
       <c r="AH32" s="1">
-        <v>0.00031223139792201007</v>
+        <v>0.00031208241436057145</v>
       </c>
       <c r="AI32" s="1">
-        <v>0.00062700927030175319</v>
+        <v>0.00062811574242035311</v>
       </c>
     </row>
     <row r="33">
@@ -3877,106 +3877,106 @@
         <v>58</v>
       </c>
       <c r="B33" s="1">
-        <v>-0.11165219050019907</v>
+        <v>-0.11155731988474095</v>
       </c>
       <c r="C33" s="1">
-        <v>-8.3857411505204268e-06</v>
+        <v>-8.3485432470863487e-06</v>
       </c>
       <c r="D33" s="1">
-        <v>-5.3401001829849002e-06</v>
+        <v>-5.3287448089275056e-06</v>
       </c>
       <c r="E33" s="1">
-        <v>3.5739417960129928e-08</v>
+        <v>3.5637235456300244e-08</v>
       </c>
       <c r="F33" s="1">
-        <v>0.00039326736813395636</v>
+        <v>0.00039329865480916722</v>
       </c>
       <c r="G33" s="1">
-        <v>0.0002514476091574786</v>
+        <v>0.000251343665151181</v>
       </c>
       <c r="H33" s="1">
-        <v>0.00039073934265809783</v>
+        <v>0.00039085327887158417</v>
       </c>
       <c r="I33" s="1">
-        <v>-8.6370272870860999e-05</v>
+        <v>-8.6228794914914968e-05</v>
       </c>
       <c r="J33" s="1">
-        <v>0.00023812772419591198</v>
+        <v>0.00023814272684841153</v>
       </c>
       <c r="K33" s="1">
-        <v>0.00031367030446644776</v>
+        <v>0.00031380229474831426</v>
       </c>
       <c r="L33" s="1">
-        <v>0.00033505175870773732</v>
+        <v>0.0003351770764789758</v>
       </c>
       <c r="M33" s="1">
-        <v>-0.0002102157684431066</v>
+        <v>-0.00020981183735673003</v>
       </c>
       <c r="N33" s="1">
-        <v>-0.00011222199347195522</v>
+        <v>-0.0001122300233948536</v>
       </c>
       <c r="O33" s="1">
-        <v>0.00027228498052549481</v>
+        <v>0.00027206934423810124</v>
       </c>
       <c r="P33" s="1">
-        <v>0.00031142654573763912</v>
+        <v>0.00031137055542476808</v>
       </c>
       <c r="Q33" s="1">
-        <v>0.00024117536479581746</v>
+        <v>0.00024130411421126405</v>
       </c>
       <c r="R33" s="1">
-        <v>-7.1954808626651257e-05</v>
+        <v>-7.1998494195376662e-05</v>
       </c>
       <c r="S33" s="1">
-        <v>-6.9498053543663946e-05</v>
+        <v>-6.9761108534720055e-05</v>
       </c>
       <c r="T33" s="1">
-        <v>-0.00010224675944311805</v>
+        <v>-0.00010236842477145567</v>
       </c>
       <c r="U33" s="1">
-        <v>-0.00029557417715979622</v>
+        <v>-0.00029573213842744046</v>
       </c>
       <c r="V33" s="1">
-        <v>1.9414487051385159e-06</v>
+        <v>2.3004398925098439e-06</v>
       </c>
       <c r="W33" s="1">
-        <v>-9.6010163130782534e-05</v>
+        <v>-9.5579285044669116e-05</v>
       </c>
       <c r="X33" s="1">
-        <v>-2.4966154561283874e-05</v>
+        <v>-2.4583298894115951e-05</v>
       </c>
       <c r="Y33" s="1">
-        <v>-3.8444874653800233e-05</v>
+        <v>-3.8001138661608634e-05</v>
       </c>
       <c r="Z33" s="1">
-        <v>-3.643446001217829e-06</v>
+        <v>-3.6744155247174436e-06</v>
       </c>
       <c r="AA33" s="1">
-        <v>-8.3823401668065738e-05</v>
+        <v>-8.3745360883607766e-05</v>
       </c>
       <c r="AB33" s="1">
-        <v>-3.9542928370614374e-05</v>
+        <v>-3.9572065897156092e-05</v>
       </c>
       <c r="AC33" s="1">
-        <v>-2.8994776501056068e-05</v>
+        <v>-2.9016860731711906e-05</v>
       </c>
       <c r="AD33" s="1">
-        <v>0.00016787332760798308</v>
+        <v>0.00016799270878013845</v>
       </c>
       <c r="AE33" s="1">
-        <v>-2.1885818613790007e-05</v>
+        <v>-2.178312243663542e-05</v>
       </c>
       <c r="AF33" s="1">
-        <v>-7.2129469137212883e-05</v>
+        <v>-7.2131143512936592e-05</v>
       </c>
       <c r="AG33" s="1">
-        <v>0.00031223139792201007</v>
+        <v>0.00031208241436057145</v>
       </c>
       <c r="AH33" s="1">
-        <v>0.0025658748331472019</v>
+        <v>0.0025656400750960779</v>
       </c>
       <c r="AI33" s="1">
-        <v>0.00090330099095109299</v>
+        <v>0.00090272721520781368</v>
       </c>
     </row>
     <row r="34">
@@ -3984,106 +3984,106 @@
         <v>59</v>
       </c>
       <c r="B34" s="1">
-        <v>-1.4619362409205052</v>
+        <v>-1.4618833055242577</v>
       </c>
       <c r="C34" s="1">
-        <v>-0.0010097613556004923</v>
+        <v>-0.0010102824590421881</v>
       </c>
       <c r="D34" s="1">
-        <v>-0.00066625676152621736</v>
+        <v>-0.0006661271581462761</v>
       </c>
       <c r="E34" s="1">
-        <v>5.6242570610441148e-06</v>
+        <v>5.6229433024775484e-06</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.0063816626722095846</v>
+        <v>-0.006381416873424613</v>
       </c>
       <c r="G34" s="1">
-        <v>-0.0049778879366692112</v>
+        <v>-0.0049790548579980113</v>
       </c>
       <c r="H34" s="1">
-        <v>-0.0060068388825839109</v>
+        <v>-0.0060069151409389548</v>
       </c>
       <c r="I34" s="1">
-        <v>-0.0083276544871487054</v>
+        <v>-0.008327474924793939</v>
       </c>
       <c r="J34" s="1">
-        <v>-0.0055623260142673454</v>
+        <v>-0.0055623877272562737</v>
       </c>
       <c r="K34" s="1">
-        <v>-0.0058567000249403105</v>
+        <v>-0.0058568792463368404</v>
       </c>
       <c r="L34" s="1">
-        <v>-0.0063754335886697898</v>
+        <v>-0.0063765035273892464</v>
       </c>
       <c r="M34" s="1">
-        <v>-0.0071928328451068332</v>
+        <v>-0.0071919325328668147</v>
       </c>
       <c r="N34" s="1">
-        <v>-0.0028232882791438436</v>
+        <v>-0.002823085037399334</v>
       </c>
       <c r="O34" s="1">
-        <v>-0.0010319212385375008</v>
+        <v>-0.0010325015778257412</v>
       </c>
       <c r="P34" s="1">
-        <v>-0.00058954971789620557</v>
+        <v>-0.00058943563110173828</v>
       </c>
       <c r="Q34" s="1">
-        <v>-0.0014858645671962465</v>
+        <v>-0.0014862610977400322</v>
       </c>
       <c r="R34" s="1">
-        <v>-0.005212041490429576</v>
+        <v>-0.0052084841819524403</v>
       </c>
       <c r="S34" s="1">
-        <v>-0.0048242525906864349</v>
+        <v>-0.0048203828815311846</v>
       </c>
       <c r="T34" s="1">
-        <v>-0.0060099414587628259</v>
+        <v>-0.0060065140391262085</v>
       </c>
       <c r="U34" s="1">
-        <v>-0.0085468179151101283</v>
+        <v>-0.0085432583502900103</v>
       </c>
       <c r="V34" s="1">
-        <v>-0.0012639579208041389</v>
+        <v>-0.0012597753793565621</v>
       </c>
       <c r="W34" s="1">
-        <v>-0.0023063401908713496</v>
+        <v>-0.0023041549506998531</v>
       </c>
       <c r="X34" s="1">
-        <v>-0.0036031634998935939</v>
+        <v>-0.0036013155387573442</v>
       </c>
       <c r="Y34" s="1">
-        <v>-0.0044680593374207571</v>
+        <v>-0.0044663483416094527</v>
       </c>
       <c r="Z34" s="1">
-        <v>1.1928478629545501e-05</v>
+        <v>1.1901767045954863e-05</v>
       </c>
       <c r="AA34" s="1">
-        <v>-1.5269908431510834e-05</v>
+        <v>-1.5302206656640392e-05</v>
       </c>
       <c r="AB34" s="1">
-        <v>-0.0003641020609104575</v>
+        <v>-0.00036521460366246592</v>
       </c>
       <c r="AC34" s="1">
-        <v>-0.0002315135107170789</v>
+        <v>-0.00023327533986443371</v>
       </c>
       <c r="AD34" s="1">
-        <v>-0.00049493725504928072</v>
+        <v>-0.00049672316567001061</v>
       </c>
       <c r="AE34" s="1">
-        <v>-0.000723857348972636</v>
+        <v>-0.00072478232261304434</v>
       </c>
       <c r="AF34" s="1">
-        <v>-0.00029877450971993826</v>
+        <v>-0.00029868492141306592</v>
       </c>
       <c r="AG34" s="1">
-        <v>0.00062700927030175319</v>
+        <v>0.00062811574242035311</v>
       </c>
       <c r="AH34" s="1">
-        <v>0.00090330099095109299</v>
+        <v>0.00090272721520781368</v>
       </c>
       <c r="AI34" s="1">
-        <v>0.039082806156102379</v>
+        <v>0.039074451962365246</v>
       </c>
     </row>
   </sheetData>
